--- a/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,84 +692,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vJqPCEPP</t>
+          <t>IViLLjPF</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45514.33333333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">merck stadion am bollenfalltor
-  darmstadt </t>
+          <t xml:space="preserve">merkur spiel arena
+  dusseldorf </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17810</v>
+        <v>54600</v>
       </c>
       <c r="F2" t="n">
-        <v>17810</v>
+        <v>36103</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>EB3q7jbk</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.79</v>
+        <v>1.09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>0.66</v>
       </c>
       <c r="M2" t="n">
+        <v>53</v>
+      </c>
+      <c r="N2" t="n">
         <v>47</v>
       </c>
-      <c r="N2" t="n">
-        <v>53</v>
-      </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q2" t="n">
         <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -786,156 +786,168 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>25.63636363636364</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>182.7272727272727</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2334090.909090909</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>73.90909090909091</v>
+      </c>
       <c r="AI2" t="n">
-        <v>26.3</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="AJ2" t="n">
-        <v>183.3</v>
+        <v>184.3636363636364</v>
       </c>
       <c r="AK2" t="n">
         <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>70.90000000000001</v>
+        <v>67.81818181818181</v>
       </c>
       <c r="AM2" t="n">
-        <v>2490000</v>
+        <v>1395454.545454545</v>
       </c>
       <c r="AN2" t="n">
-        <v>74</v>
+        <v>71.90909090909091</v>
       </c>
       <c r="AO2" t="n">
-        <v>25.6875</v>
+        <v>22.69230769230769</v>
       </c>
       <c r="AP2" t="n">
-        <v>186.25</v>
+        <v>186.3846153846154</v>
       </c>
       <c r="AQ2" t="n">
         <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>68.75</v>
+        <v>66</v>
       </c>
       <c r="AS2" t="n">
-        <v>1679687.5</v>
+        <v>1753846.153846154</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.1875</v>
+        <v>73.53846153846153</v>
       </c>
       <c r="AU2" t="n">
-        <v>21.95454545454545</v>
+        <v>23.3125</v>
       </c>
       <c r="AV2" t="n">
-        <v>186.4545454545455</v>
+        <v>181</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>64.04545454545455</v>
+        <v>65.25</v>
       </c>
       <c r="AY2" t="n">
-        <v>1346590.909090909</v>
+        <v>1126250</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.95454545454545</v>
+        <v>72.5625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2Hl43AnC</t>
+          <t>tC1Aa08D</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45514.33333333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">sportpark ronhof thomas sommer
-  furth </t>
+          <t xml:space="preserve">waldstadion kaiserlinde
+  spiesen elversberg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16626</v>
+        <v>9970</v>
       </c>
       <c r="F3" t="n">
-        <v>12664</v>
+        <v>9502</v>
       </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="M3" t="n">
+        <v>45</v>
+      </c>
+      <c r="N3" t="n">
+        <v>55</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10</v>
+      </c>
+      <c r="P3" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="M3" t="n">
-        <v>47</v>
-      </c>
-      <c r="N3" t="n">
-        <v>53</v>
-      </c>
-      <c r="O3" t="n">
-        <v>22</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>9</v>
       </c>
-      <c r="R3" t="n">
-        <v>5</v>
-      </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -950,154 +962,166 @@
       <c r="Z3" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
       <c r="AC3" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>183.1</v>
+        <v>182.3</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="AG3" t="n">
-        <v>1480000</v>
+        <v>1200000</v>
       </c>
       <c r="AH3" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
+        <v>70.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>185.4545454545455</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>71.27272727272727</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>4545454.545454546</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>78.63636363636364</v>
+      </c>
       <c r="AO3" t="n">
-        <v>22.72727272727273</v>
+        <v>25.30769230769231</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.5454545454545</v>
+        <v>182.3076923076923</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>64.59090909090909</v>
+        <v>65.23076923076923</v>
       </c>
       <c r="AS3" t="n">
-        <v>1273863.636363636</v>
+        <v>975000</v>
       </c>
       <c r="AT3" t="n">
-        <v>72.86363636363636</v>
+        <v>69.07692307692308</v>
       </c>
       <c r="AU3" t="n">
-        <v>25.57142857142857</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AV3" t="n">
-        <v>181.8571428571429</v>
+        <v>186.5714285714286</v>
       </c>
       <c r="AW3" t="n">
-        <v>1</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="AX3" t="n">
-        <v>66.71428571428571</v>
+        <v>69.47619047619048</v>
       </c>
       <c r="AY3" t="n">
-        <v>1175000</v>
+        <v>2787619.047619048</v>
       </c>
       <c r="AZ3" t="n">
-        <v>68.42857142857143</v>
+        <v>73.19047619047619</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SIOxI915</t>
+          <t>YJ3eN30K</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45508.35416666666</v>
+        <v>45514.33333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">winter n 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">max morlock stadion
+  nuremberg </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19500</v>
+        <v>44308</v>
       </c>
       <c r="F4" t="n">
-        <v>17400</v>
+        <v>50000</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.98</v>
+        <v>0.93</v>
       </c>
       <c r="L4" t="n">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="M4" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
+        <v>8</v>
+      </c>
+      <c r="P4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>11</v>
+      </c>
+      <c r="T4" t="n">
         <v>12</v>
       </c>
-      <c r="P4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>3</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>12</v>
-      </c>
-      <c r="T4" t="n">
-        <v>16</v>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1112,138 +1136,170 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>22.77777777777778</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>182</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>66</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1697222.222222222</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>72.55555555555556</v>
+      </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>25.625</v>
       </c>
       <c r="AJ4" t="n">
-        <v>184.6363636363636</v>
+        <v>189.75</v>
       </c>
       <c r="AK4" t="n">
         <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>67.63636363636364</v>
+        <v>67.625</v>
       </c>
       <c r="AM4" t="n">
-        <v>1484090.909090909</v>
+        <v>1540625</v>
       </c>
       <c r="AN4" t="n">
-        <v>70.63636363636364</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>71.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>28.125</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>180</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>67.875</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1209375</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>70</v>
+      </c>
       <c r="AU4" t="n">
-        <v>25.22222222222222</v>
+        <v>26.57142857142857</v>
       </c>
       <c r="AV4" t="n">
-        <v>180.9444444444445</v>
+        <v>186.7142857142857</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>67.5</v>
+        <v>68.57142857142857</v>
       </c>
       <c r="AY4" t="n">
-        <v>1468055.555555556</v>
+        <v>1428571.428571429</v>
       </c>
       <c r="AZ4" t="n">
-        <v>71.11111111111111</v>
+        <v>70.57142857142857</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EeIMLi2t</t>
+          <t>h4pSHsOs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45507.64583333334</v>
+        <v>45513.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">veltins arena
-  gelsenkirchen </t>
+          <t xml:space="preserve">fritz walter stadion
+  kaiserslautern </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>62271</v>
+        <v>49500</v>
       </c>
       <c r="F5" t="n">
-        <v>61000</v>
+        <v>41632</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="K5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L5" t="n">
         <v>2.7</v>
       </c>
-      <c r="L5" t="n">
-        <v>1.21</v>
-      </c>
       <c r="M5" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
+        <v>13</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
         <v>14</v>
       </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T5" t="n">
-        <v>11</v>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>4bJLk19p</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1258,170 +1314,166 @@
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="AC5" t="n">
-        <v>26.25</v>
+        <v>25</v>
       </c>
       <c r="AD5" t="n">
-        <v>187.125</v>
+        <v>184.6363636363636</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>69</v>
+        <v>67.63636363636364</v>
       </c>
       <c r="AG5" t="n">
-        <v>1740625</v>
+        <v>1484090.909090909</v>
       </c>
       <c r="AH5" t="n">
-        <v>71.5</v>
+        <v>70.63636363636364</v>
       </c>
       <c r="AI5" t="n">
-        <v>25.375</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>183.25</v>
+        <v>183.1</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AL5" t="n">
-        <v>66.875</v>
+        <v>67</v>
       </c>
       <c r="AM5" t="n">
-        <v>1287500</v>
+        <v>1480000</v>
       </c>
       <c r="AN5" t="n">
-        <v>71.875</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>27.22222222222222</v>
+        <v>25.23529411764706</v>
       </c>
       <c r="AP5" t="n">
-        <v>190.2222222222222</v>
+        <v>181.4705882352941</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>67.94444444444444</v>
+        <v>68.05882352941177</v>
       </c>
       <c r="AS5" t="n">
-        <v>1294444.444444444</v>
+        <v>1691176.470588235</v>
       </c>
       <c r="AT5" t="n">
-        <v>70.88888888888889</v>
+        <v>71.29411764705883</v>
       </c>
       <c r="AU5" t="n">
-        <v>24.57142857142857</v>
+        <v>23.13636363636364</v>
       </c>
       <c r="AV5" t="n">
-        <v>184.9285714285714</v>
+        <v>183.8181818181818</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>66.07142857142857</v>
+        <v>65.31818181818181</v>
       </c>
       <c r="AY5" t="n">
-        <v>1302142.857142857</v>
+        <v>1430681.818181818</v>
       </c>
       <c r="AZ5" t="n">
-        <v>71.14285714285714</v>
+        <v>73.09090909090909</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fiod5WHa</t>
+          <t>StuiCwhJ</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45507.33333333334</v>
+        <v>45513.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">benen l 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">heinz von heiden arena
-  hannover </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>49200</v>
+        <v>15210</v>
       </c>
       <c r="F6" t="n">
-        <v>31800</v>
+        <v>12095</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>0.74</v>
       </c>
       <c r="L6" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="N6" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="O6" t="n">
+        <v>8</v>
+      </c>
+      <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>22</v>
+      </c>
+      <c r="T6" t="n">
         <v>16</v>
       </c>
-      <c r="P6" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>12</v>
-      </c>
-      <c r="T6" t="n">
-        <v>17</v>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1436,743 +1488,43 @@
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>184.3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2082500</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>73.59999999999999</v>
-      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="n">
-        <v>24.40909090909091</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>183.4545454545455</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>68</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1812500</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>72.81818181818181</v>
-      </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>OWxD1lHO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45507.33333333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">haslberger w 
-  ger </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">olympiastadion
-  berlin </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>74667</v>
-      </c>
-      <c r="F7" t="n">
-        <v>48591</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2y0u8Wrq</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>57</v>
-      </c>
-      <c r="N7" t="n">
-        <v>43</v>
-      </c>
-      <c r="O7" t="n">
-        <v>10</v>
-      </c>
-      <c r="P7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>16</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>YmfcAeCo</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0AI1QUJH</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>59</v>
-      </c>
-      <c r="X7" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="n">
-        <v>23.22222222222222</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>183.7777777777778</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>69.44444444444444</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2422222.222222222</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>76.11111111111111</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>25.125</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>183.625</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>67</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1356250</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>72</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>23.55</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>184.2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2360000</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>74.75</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>24.9375</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>186.1875</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>66.9375</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1417187.5</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>72.125</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>zkVf7hmm</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45507.33333333334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">braun r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bbbank wildpark
-  karlsruhe </t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>34302</v>
-      </c>
-      <c r="F8" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>2</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="M8" t="n">
-        <v>51</v>
-      </c>
-      <c r="N8" t="n">
-        <v>49</v>
-      </c>
-      <c r="O8" t="n">
-        <v>15</v>
-      </c>
-      <c r="P8" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>5</v>
-      </c>
-      <c r="S8" t="n">
-        <v>15</v>
-      </c>
-      <c r="T8" t="n">
-        <v>12</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>OzPMRhK3</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>59</v>
-      </c>
-      <c r="X8" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="AC8" t="n">
-        <v>26.27272727272727</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>184.3636363636364</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>67.81818181818181</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1395454.545454545</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>71.90909090909091</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>22.77777777777778</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>182</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>66</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>72.55555555555556</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>22.78947368421053</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>181.1052631578947</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>64.84210526315789</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1087894.736842105</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>72.84210526315789</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>27.77777777777778</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>181.2222222222222</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>67.44444444444444</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1377777.777777778</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>70.22222222222223</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>f5QUJVWh</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45507.33333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heft f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mdcc arena
-  magdeburg </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>30098</v>
-      </c>
-      <c r="F9" t="n">
-        <v>21469</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="M9" t="n">
-        <v>63</v>
-      </c>
-      <c r="N9" t="n">
-        <v>37</v>
-      </c>
-      <c r="O9" t="n">
-        <v>21</v>
-      </c>
-      <c r="P9" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>11</v>
-      </c>
-      <c r="T9" t="n">
-        <v>8</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>IgZoGKFn</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>8E8qmw3d</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>59</v>
-      </c>
-      <c r="X9" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="AN9" t="n">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>183</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>62</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>887500</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>70.5</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>24.93333333333333</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>176.3333333333333</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>181.4666666666667</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>64.93333333333334</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>908333.3333333334</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>68.26666666666667</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>OA1xkBXI</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45506.64583333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rheinenergiestadion
-  cologne </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M10" t="n">
-        <v>58</v>
-      </c>
-      <c r="N10" t="n">
-        <v>42</v>
-      </c>
-      <c r="O10" t="n">
-        <v>26</v>
-      </c>
-      <c r="P10" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6</v>
-      </c>
-      <c r="S10" t="n">
-        <v>18</v>
-      </c>
-      <c r="T10" t="n">
-        <v>7</v>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>4fX0k7gg</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>EDRZkDzS</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>59</v>
-      </c>
-      <c r="X10" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="AC10" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>186</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4680000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>79</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>183.4</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>71.2</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>2470000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>25.78947368421053</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>184.7894736842105</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.210526315789474</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>68.63157894736842</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2486315.789473684</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>73.05263157894737</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>183.25</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>69.05</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>2124000</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>72.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:BG32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,88 +688,123 @@
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IViLLjPF</t>
+          <t>QHrzGLhf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45515.35416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">merkur spiel arena
-  dusseldorf </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54600</v>
+        <v>23325</v>
       </c>
       <c r="F2" t="n">
-        <v>36103</v>
+        <v>22791</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.09</v>
+        <v>2.15</v>
       </c>
       <c r="L2" t="n">
-        <v>0.66</v>
+        <v>2.4</v>
       </c>
       <c r="M2" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O2" t="n">
         <v>20</v>
       </c>
       <c r="P2" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" t="n">
         <v>9</v>
       </c>
-      <c r="Q2" t="n">
-        <v>6</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>OzPMRhK3</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -786,168 +821,159 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>25.63636363636364</v>
+        <v>25.625</v>
       </c>
       <c r="AD2" t="n">
-        <v>182.7272727272727</v>
+        <v>186.125</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AF2" t="n">
-        <v>70</v>
+        <v>67.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>2334090.909090909</v>
+        <v>1428125</v>
       </c>
       <c r="AH2" t="n">
-        <v>73.90909090909091</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>26.27272727272727</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>184.3636363636364</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>67.81818181818181</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1395454.545454545</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>71.90909090909091</v>
-      </c>
+        <v>71.25</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>22.69230769230769</v>
+        <v>25.1875</v>
       </c>
       <c r="AP2" t="n">
-        <v>186.3846153846154</v>
+        <v>182</v>
       </c>
       <c r="AQ2" t="n">
         <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>66</v>
+        <v>66.8125</v>
       </c>
       <c r="AS2" t="n">
-        <v>1753846.153846154</v>
+        <v>1287500</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.53846153846153</v>
+        <v>70.9375</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.3125</v>
+        <v>24.73684210526316</v>
       </c>
       <c r="AV2" t="n">
-        <v>181</v>
+        <v>178.7368421052632</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>65.25</v>
+        <v>67.36842105263158</v>
       </c>
       <c r="AY2" t="n">
-        <v>1126250</v>
+        <v>1485526.315789474</v>
       </c>
       <c r="AZ2" t="n">
-        <v>72.5625</v>
-      </c>
+        <v>70.26315789473684</v>
+      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tC1Aa08D</t>
+          <t>KdD11Mw1</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45515.35416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bauer t 
+          <t xml:space="preserve">schwengers p 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waldstadion kaiserlinde
-  spiesen elversberg </t>
+          <t xml:space="preserve">home deluxe arena
+  paderborn </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9970</v>
+        <v>15000</v>
       </c>
       <c r="F3" t="n">
-        <v>9502</v>
+        <v>12972</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.45</v>
+        <v>1.62</v>
       </c>
       <c r="L3" t="n">
-        <v>3.39</v>
+        <v>1.05</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
       <c r="W3" t="n">
@@ -965,163 +991,158 @@
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="AC3" t="n">
-        <v>24.9</v>
+        <v>25.125</v>
       </c>
       <c r="AD3" t="n">
-        <v>182.3</v>
+        <v>183.625</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>66.90000000000001</v>
+        <v>67</v>
       </c>
       <c r="AG3" t="n">
-        <v>1200000</v>
+        <v>1356250</v>
       </c>
       <c r="AH3" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>185.4545454545455</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>71.27272727272727</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>4545454.545454546</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>78.63636363636364</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>25.30769230769231</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="AP3" t="n">
-        <v>182.3076923076923</v>
+        <v>186.1111111111111</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>65.23076923076923</v>
+        <v>67.22222222222223</v>
       </c>
       <c r="AS3" t="n">
-        <v>975000</v>
+        <v>1555555.555555556</v>
       </c>
       <c r="AT3" t="n">
-        <v>69.07692307692308</v>
+        <v>72.55555555555556</v>
       </c>
       <c r="AU3" t="n">
-        <v>26.33333333333333</v>
+        <v>24.27777777777778</v>
       </c>
       <c r="AV3" t="n">
-        <v>186.5714285714286</v>
+        <v>184.8888888888889</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.380952380952381</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>69.47619047619048</v>
+        <v>68.44444444444444</v>
       </c>
       <c r="AY3" t="n">
-        <v>2787619.047619048</v>
+        <v>1895833.333333333</v>
       </c>
       <c r="AZ3" t="n">
-        <v>73.19047619047619</v>
-      </c>
+        <v>73.66666666666667</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YJ3eN30K</t>
+          <t>MqxqEaN6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45515.35416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">winter n 
+          <t xml:space="preserve">erbst l 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">max morlock stadion
-  nuremberg </t>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44308</v>
+        <v>12794</v>
       </c>
       <c r="F4" t="n">
-        <v>50000</v>
+        <v>12422</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.93</v>
+        <v>1.48</v>
       </c>
       <c r="L4" t="n">
-        <v>2.12</v>
+        <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T4" t="n">
         <v>11</v>
       </c>
-      <c r="T4" t="n">
-        <v>12</v>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1136,170 +1157,161 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>22.77777777777778</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>182</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>66</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>72.55555555555556</v>
-      </c>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>25.625</v>
+        <v>26.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>189.75</v>
+        <v>184.3</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AL4" t="n">
-        <v>67.625</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="AM4" t="n">
-        <v>1540625</v>
+        <v>2082500</v>
       </c>
       <c r="AN4" t="n">
-        <v>71.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>28.125</v>
+        <v>25.57142857142857</v>
       </c>
       <c r="AP4" t="n">
-        <v>180</v>
+        <v>181.8571428571429</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>67.875</v>
+        <v>66.71428571428571</v>
       </c>
       <c r="AS4" t="n">
-        <v>1209375</v>
+        <v>1175000</v>
       </c>
       <c r="AT4" t="n">
-        <v>70</v>
+        <v>68.42857142857143</v>
       </c>
       <c r="AU4" t="n">
-        <v>26.57142857142857</v>
+        <v>24.17391304347826</v>
       </c>
       <c r="AV4" t="n">
-        <v>186.7142857142857</v>
+        <v>183.5652173913043</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>68.57142857142857</v>
+        <v>67.56521739130434</v>
       </c>
       <c r="AY4" t="n">
-        <v>1428571.428571429</v>
+        <v>1753260.869565217</v>
       </c>
       <c r="AZ4" t="n">
-        <v>70.57142857142857</v>
-      </c>
+        <v>72.60869565217391</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pSHsOs</t>
+          <t>CW9g3r9l</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45514.64583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz walter stadion
-  kaiserslautern </t>
+          <t xml:space="preserve">volksparkstadion
+  hamburg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49500</v>
+        <v>57274</v>
       </c>
       <c r="F5" t="n">
-        <v>41632</v>
+        <v>57000</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.02</v>
+        <v>1.35</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7</v>
+        <v>0.93</v>
       </c>
       <c r="M5" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="N5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="O5" t="n">
         <v>13</v>
       </c>
       <c r="P5" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
+        <v>4</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9</v>
+      </c>
+      <c r="T5" t="n">
         <v>8</v>
       </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="n">
-        <v>14</v>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -1314,194 +1326,213 @@
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>25</v>
+        <v>25.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>184.6363636363636</v>
+        <v>183.4</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
       </c>
       <c r="AF5" t="n">
-        <v>67.63636363636364</v>
+        <v>71.2</v>
       </c>
       <c r="AG5" t="n">
-        <v>1484090.909090909</v>
+        <v>2470000</v>
       </c>
       <c r="AH5" t="n">
-        <v>70.63636363636364</v>
+        <v>73.7</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>22.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>183.1</v>
+        <v>183.3</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>67</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AM5" t="n">
-        <v>1480000</v>
+        <v>2420000</v>
       </c>
       <c r="AN5" t="n">
-        <v>71.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AO5" t="n">
-        <v>25.23529411764706</v>
+        <v>25.70588235294118</v>
       </c>
       <c r="AP5" t="n">
-        <v>181.4705882352941</v>
+        <v>184.5294117647059</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>68.05882352941177</v>
+        <v>70.23529411764706</v>
       </c>
       <c r="AS5" t="n">
-        <v>1691176.470588235</v>
+        <v>2645882.352941176</v>
       </c>
       <c r="AT5" t="n">
-        <v>71.29411764705883</v>
+        <v>73.05882352941177</v>
       </c>
       <c r="AU5" t="n">
-        <v>23.13636363636364</v>
+        <v>23.56521739130435</v>
       </c>
       <c r="AV5" t="n">
-        <v>183.8181818181818</v>
+        <v>184.2173913043478</v>
       </c>
       <c r="AW5" t="n">
         <v>1</v>
       </c>
       <c r="AX5" t="n">
-        <v>65.31818181818181</v>
+        <v>68.43478260869566</v>
       </c>
       <c r="AY5" t="n">
-        <v>1430681.818181818</v>
+        <v>1948913.043478261</v>
       </c>
       <c r="AZ5" t="n">
-        <v>73.09090909090909</v>
-      </c>
+        <v>74.39130434782609</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>StuiCwhJ</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">benen l 
+          <t xml:space="preserve">oldhafer k 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15210</v>
+        <v>10059</v>
       </c>
       <c r="F6" t="n">
-        <v>12095</v>
+        <v>4637</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>hjNlCFPB</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.47</v>
-      </c>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N6" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
         <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>KW0bzbwJ</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>OzPMRhK3</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>59</v>
       </c>
       <c r="X6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+      <c r="AI6" t="n">
+        <v>26.18181818181818</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>183.0909090909091</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1413636.363636364</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>71.72727272727273</v>
+      </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
@@ -1509,22 +1540,4065 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
+        <v>25.21428571428572</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>66.21428571428571</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1071071.428571429</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>70.92857142857143</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>13696</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12959</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>rXqBh2xP</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>31</v>
+      </c>
+      <c r="N7" t="n">
+        <v>69</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>12</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>UqphGQrg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>59</v>
+      </c>
+      <c r="X7" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>71.625</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2912500</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>74.75</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="n">
+        <v>26.68421052631579</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>186.6315789473684</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>70.57894736842105</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>2598947.368421053</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>72.63157894736842</v>
+      </c>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>32249</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>zL1YsOi1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>46</v>
+      </c>
+      <c r="N8" t="n">
+        <v>54</v>
+      </c>
+      <c r="O8" t="n">
+        <v>19</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4YhTfKrD</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>59</v>
+      </c>
+      <c r="X8" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>183.8181818181818</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>69.54545454545455</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2061363.636363636</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>73.36363636363636</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>180.1428571428571</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>65.57142857142857</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>853571.4285714285</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>67.28571428571429</v>
+      </c>
+      <c r="AU8" t="n">
         <v>21.5</v>
       </c>
-      <c r="AV6" t="n">
-        <v>183</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX6" t="n">
+      <c r="AV8" t="n">
+        <v>186.95</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1241250</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">speckner m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>tW75B1ei</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>37</v>
+      </c>
+      <c r="N9" t="n">
+        <v>63</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S9" t="n">
+        <v>13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>17</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>4tvZg2Br</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>59</v>
+      </c>
+      <c r="X9" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>24.15789473684211</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>186.3684210526316</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>66.89473684210526</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1414473.684210526</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>72.31578947368421</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>25600</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KIHmtCkL</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>36</v>
+      </c>
+      <c r="N10" t="n">
+        <v>64</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6</v>
+      </c>
+      <c r="S10" t="n">
+        <v>17</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>G8THUSaE</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>59</v>
+      </c>
+      <c r="X10" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1040625</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>69.125</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>2340000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>181.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>64</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>997500</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>23.47368421052632</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>186.3684210526316</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>68.47368421052632</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1956578.947368421</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>75</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nouhoum a 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5186</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>E3xs5mIe</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>31</v>
+      </c>
+      <c r="N11" t="n">
+        <v>69</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>9</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>bJ0lIKrp</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>59</v>
+      </c>
+      <c r="X11" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>184</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1177500</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="n">
+        <v>26.26315789473684</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>181</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>65.78947368421052</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>959210.5263157894</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>67.52631578947368</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>15210</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12581</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>35</v>
+      </c>
+      <c r="N12" t="n">
+        <v>65</v>
+      </c>
+      <c r="O12" t="n">
+        <v>19</v>
+      </c>
+      <c r="P12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="n">
+        <v>20</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>59</v>
+      </c>
+      <c r="X12" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>183.4444444444445</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>70.88888888888889</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2213888.888888889</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>73.44444444444444</v>
+      </c>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="n">
+        <v>22.875</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>183.875</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>67.25</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1814062.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>75.8125</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15414</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9705</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>UZxEj1R4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>54</v>
+      </c>
+      <c r="N13" t="n">
+        <v>46</v>
+      </c>
+      <c r="O13" t="n">
+        <v>16</v>
+      </c>
+      <c r="P13" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>14</v>
+      </c>
+      <c r="S13" t="n">
+        <v>18</v>
+      </c>
+      <c r="T13" t="n">
+        <v>24</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>rZtwKVAL</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>4fX0k7gg</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>59</v>
+      </c>
+      <c r="X13" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>184.6</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>3820000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="n">
+        <v>26.04761904761905</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>187.5714285714286</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.238095238095238</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>68.42857142857143</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>2287619.047619048</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>72.23809523809524</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lechner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6487</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>WrbkcjCd</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>31</v>
+      </c>
+      <c r="N14" t="n">
+        <v>69</v>
+      </c>
+      <c r="O14" t="n">
+        <v>10</v>
+      </c>
+      <c r="P14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>3</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="n">
+        <v>12</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>lC9J1RTa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>59</v>
+      </c>
+      <c r="X14" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>189</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>70.35714285714286</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1908928.571428571</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>73.71428571428571</v>
+      </c>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ludwigspark stadion
+  saarbrucken </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>16003</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14868</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>fLbhmJ5l</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>44</v>
+      </c>
+      <c r="N15" t="n">
+        <v>56</v>
+      </c>
+      <c r="O15" t="n">
+        <v>7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="n">
+        <v>21</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>trS1MB7T</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>59</v>
+      </c>
+      <c r="X15" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>182.875</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1521875</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>72.25</v>
+      </c>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>178</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>69.16666666666667</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1866666.666666667</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45522.33333333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weisbach e 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>19708</v>
+      </c>
+      <c r="F16" t="n">
+        <v>5504</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>UNr2EUfd</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>24</v>
+      </c>
+      <c r="N16" t="n">
+        <v>76</v>
+      </c>
+      <c r="O16" t="n">
+        <v>5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>CCww5Qfo</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>59</v>
+      </c>
+      <c r="X16" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>185.125</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4975000</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>182.1904761904762</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.476190476190476</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>72.19047619047619</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>4629761.904761905</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>76.95238095238095</v>
+      </c>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>31026</v>
+      </c>
+      <c r="F17" t="n">
+        <v>29555</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>j3PKcB4E</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>39</v>
+      </c>
+      <c r="N17" t="n">
+        <v>61</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T17" t="n">
+        <v>13</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SfKt2E6n</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>59</v>
+      </c>
+      <c r="X17" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1760000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="n">
+        <v>24.4375</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>186.3125</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1476562.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>27332</v>
+      </c>
+      <c r="F18" t="n">
+        <v>26044</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>pp38UXK8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>44</v>
+      </c>
+      <c r="N18" t="n">
+        <v>56</v>
+      </c>
+      <c r="O18" t="n">
+        <v>12</v>
+      </c>
+      <c r="P18" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>21</v>
+      </c>
+      <c r="T18" t="n">
+        <v>24</v>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>KrFXELrR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>59</v>
+      </c>
+      <c r="X18" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>184</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1932500</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>186.1428571428571</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>65.28571428571429</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1321428.571428571</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>72.28571428571429</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>25.09523809523809</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.047619047619048</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>69.04761904761905</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1947619.047619048</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>72.95238095238095</v>
+      </c>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45521.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksparkstadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>57274</v>
+      </c>
+      <c r="F19" t="n">
+        <v>50971</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>I1Vk6k3R</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>20</v>
+      </c>
+      <c r="N19" t="n">
+        <v>80</v>
+      </c>
+      <c r="O19" t="n">
+        <v>7</v>
+      </c>
+      <c r="P19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>9</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="n">
+        <v>5</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>AgnJojCs</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>59</v>
+      </c>
+      <c r="X19" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>186.1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>81</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>34700000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="n">
+        <v>23.61904761904762</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>183.7142857142857</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>1.619047619047619</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>76.80952380952381</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>21880952.38095238</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>83.0952380952381</v>
+      </c>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>14500</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10850</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Oh2C15j0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>32</v>
+      </c>
+      <c r="N20" t="n">
+        <v>68</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4</v>
+      </c>
+      <c r="P20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
+        <v>8</v>
+      </c>
+      <c r="S20" t="n">
+        <v>17</v>
+      </c>
+      <c r="T20" t="n">
+        <v>16</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>8bJFOfzK</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>59</v>
+      </c>
+      <c r="X20" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="n">
+        <v>25.28571428571428</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>188.5714285714286</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>66.14285714285714</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1089285.714285714</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>70.28571428571429</v>
+      </c>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benen l 
+  ger </t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4990</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4990</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Q1yNyI5t</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>39</v>
+      </c>
+      <c r="N21" t="n">
+        <v>61</v>
+      </c>
+      <c r="O21" t="n">
+        <v>6</v>
+      </c>
+      <c r="P21" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>5</v>
+      </c>
+      <c r="S21" t="n">
+        <v>6</v>
+      </c>
+      <c r="T21" t="n">
+        <v>12</v>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Wbz1kusU</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>59</v>
+      </c>
+      <c r="X21" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>185.5555555555555</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>75.44444444444444</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>7833333.333333333</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>77.22222222222223</v>
+      </c>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="n">
+        <v>25.69565217391304</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>184.304347826087</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.391304347826087</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>71.65217391304348</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4054347.826086957</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>76.30434782608695</v>
+      </c>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">audi sportpark
+  ingolstadt </t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>15800</v>
+      </c>
+      <c r="F22" t="n">
+        <v>11655</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ne5QkLtB</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>45</v>
+      </c>
+      <c r="N22" t="n">
+        <v>55</v>
+      </c>
+      <c r="O22" t="n">
+        <v>13</v>
+      </c>
+      <c r="P22" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>10</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>19</v>
+      </c>
+      <c r="T22" t="n">
+        <v>14</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>CWcD8UM8</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>59</v>
+      </c>
+      <c r="X22" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1750000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>182.95</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1510000</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>70.34999999999999</v>
+      </c>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>20352</v>
+      </c>
+      <c r="F23" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EB0xsr77</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>41</v>
+      </c>
+      <c r="N23" t="n">
+        <v>59</v>
+      </c>
+      <c r="O23" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>9</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="n">
+        <v>9</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>0KMe4S4D</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>59</v>
+      </c>
+      <c r="X23" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>183.2727272727273</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2.090909090909091</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>79.81818181818181</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>26636363.63636364</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>83.36363636363636</v>
+      </c>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="n">
+        <v>23.15384615384615</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>184.2307692307692</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.769230769230769</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>76.92307692307692</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>22559615.38461538</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>81.84615384615384</v>
+      </c>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>16667</v>
+      </c>
+      <c r="F24" t="n">
+        <v>15500</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>88Xgj1Y5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>49</v>
+      </c>
+      <c r="N24" t="n">
+        <v>51</v>
+      </c>
+      <c r="O24" t="n">
+        <v>8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6</v>
+      </c>
+      <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>59</v>
+      </c>
+      <c r="X24" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="n">
+        <v>25.88888888888889</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>183.3333333333333</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>75.11111111111111</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>10033333.33333333</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>77.44444444444444</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>22.27272727272727</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>186.4545454545455</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>62.90909090909091</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>863636.3636363636</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>72</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>26.95652173913043</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>182.1304347826087</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.608695652173913</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>74.08695652173913</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>6278260.869565218</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>76.04347826086956</v>
+      </c>
+      <c r="BA24" t="inlineStr"/>
+      <c r="BB24" t="inlineStr"/>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr"/>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr"/>
+      <c r="BG24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45521.4375</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">michel f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F25" t="n">
+        <v>6800</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>lKLJUxeT</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>33</v>
+      </c>
+      <c r="N25" t="n">
+        <v>67</v>
+      </c>
+      <c r="O25" t="n">
+        <v>6</v>
+      </c>
+      <c r="P25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
+        <v>9</v>
+      </c>
+      <c r="S25" t="n">
+        <v>7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>59</v>
+      </c>
+      <c r="X25" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="n">
+        <v>26.25</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>188.25</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>72.125</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>2837500</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>187.1111111111111</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>69.77777777777777</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>2063888.888888889</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>72.61111111111111</v>
+      </c>
+      <c r="BA25" t="inlineStr"/>
+      <c r="BB25" t="inlineStr"/>
+      <c r="BC25" t="inlineStr"/>
+      <c r="BD25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="inlineStr"/>
+      <c r="BG25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>16485</v>
+      </c>
+      <c r="F26" t="n">
+        <v>14811</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>vsXIDreP</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>53</v>
+      </c>
+      <c r="N26" t="n">
+        <v>47</v>
+      </c>
+      <c r="O26" t="n">
+        <v>8</v>
+      </c>
+      <c r="P26" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>9</v>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>rPfNaCdg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>59</v>
+      </c>
+      <c r="X26" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>184</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>75.27272727272727</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>9627272.727272727</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>79</v>
+      </c>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AU26" t="n">
+        <v>24.43478260869565</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>185.4347826086957</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.347826086956522</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>73.47826086956522</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>7100000</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>77.95652173913044</v>
+      </c>
+      <c r="BA26" t="inlineStr"/>
+      <c r="BB26" t="inlineStr"/>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="inlineStr"/>
+      <c r="BG26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45521.33333333334</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prigan f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>7134</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4235</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>WzEYqEyg</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>35</v>
+      </c>
+      <c r="N27" t="n">
+        <v>65</v>
+      </c>
+      <c r="O27" t="n">
+        <v>4</v>
+      </c>
+      <c r="P27" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>pvucOaW7</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>59</v>
+      </c>
+      <c r="X27" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>183.3</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AU27" t="n">
+        <v>22.60869565217391</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>183.2173913043478</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>64.08695652173913</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1201086.956521739</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>72.73913043478261</v>
+      </c>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
+      <c r="BC27" t="inlineStr"/>
+      <c r="BD27" t="inlineStr"/>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="inlineStr"/>
+      <c r="BG27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>19500</v>
+      </c>
+      <c r="F28" t="n">
+        <v>17400</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>tbC3EcQn</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>27</v>
+      </c>
+      <c r="N28" t="n">
+        <v>73</v>
+      </c>
+      <c r="O28" t="n">
+        <v>5</v>
+      </c>
+      <c r="P28" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>5</v>
+      </c>
+      <c r="S28" t="n">
+        <v>11</v>
+      </c>
+      <c r="T28" t="n">
+        <v>11</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>59</v>
+      </c>
+      <c r="X28" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="n">
+        <v>25.81818181818182</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>183.5454545454545</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.727272727272727</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>81.18181818181819</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>37700000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>85.18181818181819</v>
+      </c>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AU28" t="n">
+        <v>25.35294117647059</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>184.6470588235294</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>3.176470588235294</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>82.41176470588235</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>55613235.29411764</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>85.52941176470588</v>
+      </c>
+      <c r="BA28" t="inlineStr"/>
+      <c r="BB28" t="inlineStr"/>
+      <c r="BC28" t="inlineStr"/>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="inlineStr"/>
+      <c r="BG28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>15057</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>boX3cIQa</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>34</v>
+      </c>
+      <c r="N29" t="n">
+        <v>66</v>
+      </c>
+      <c r="O29" t="n">
+        <v>9</v>
+      </c>
+      <c r="P29" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>8</v>
+      </c>
+      <c r="S29" t="n">
+        <v>14</v>
+      </c>
+      <c r="T29" t="n">
+        <v>12</v>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>02hM7hzd</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>59</v>
+      </c>
+      <c r="X29" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>185.8888888888889</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>70.22222222222223</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>2277777.777777778</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>73.77777777777777</v>
+      </c>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="n">
+        <v>23.94444444444444</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>183.9444444444445</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>68.38888888888889</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1944444.444444444</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>73.33333333333333</v>
+      </c>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr"/>
+      <c r="BG29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brita arena
+  wiesbaden </t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>12566</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12500</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ObxFt3lm</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>35</v>
+      </c>
+      <c r="N30" t="n">
+        <v>65</v>
+      </c>
+      <c r="O30" t="n">
+        <v>8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6</v>
+      </c>
+      <c r="S30" t="n">
+        <v>19</v>
+      </c>
+      <c r="T30" t="n">
+        <v>18</v>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>59</v>
+      </c>
+      <c r="X30" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>6100000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>24.53846153846154</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>183.3846153846154</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>63.76923076923077</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>769230.7692307692</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>67.23076923076923</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>71</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>3146250</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="inlineStr"/>
+      <c r="BG30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>13090</v>
+      </c>
+      <c r="F31" t="n">
+        <v>12000</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>nVM1YUFj</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>31</v>
+      </c>
+      <c r="N31" t="n">
+        <v>69</v>
+      </c>
+      <c r="O31" t="n">
+        <v>9</v>
+      </c>
+      <c r="P31" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>8</v>
+      </c>
+      <c r="S31" t="n">
+        <v>11</v>
+      </c>
+      <c r="T31" t="n">
+        <v>13</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>lEwgk7go</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>59</v>
+      </c>
+      <c r="X31" t="n">
+        <v>593</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>186.8888888888889</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>73.22222222222223</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>7694444.444444444</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>76.88888888888889</v>
+      </c>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AU31" t="n">
+        <v>23.94117647058824</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>184.4117647058823</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.529411764705882</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>72.05882352941177</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>7377941.176470588</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>78.58823529411765</v>
+      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
+      <c r="BC31" t="inlineStr"/>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="inlineStr"/>
+      <c r="BF31" t="inlineStr"/>
+      <c r="BG31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F32" t="n">
+        <v>30210</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M32" t="n">
+        <v>38</v>
+      </c>
+      <c r="N32" t="n">
         <v>62</v>
       </c>
-      <c r="AY6" t="n">
-        <v>887500</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>70.5</v>
+      <c r="O32" t="n">
+        <v>12</v>
+      </c>
+      <c r="P32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="n">
+        <v>20</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>59</v>
+      </c>
+      <c r="X32" t="n">
+        <v>594</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2024</v>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="AC32" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>184.625</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>25375000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>83.75</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>9810000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>181.8571428571429</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>2.190476190476191</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>82.0952380952381</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>50242857.14285714</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>85.0952380952381</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>23.27777777777778</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>72.16666666666667</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>6294444.444444444</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>78.05555555555556</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>191.75</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>289</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>23600000</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,210 +480,200 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_home</t>
+          <t>ball_possession_home</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_away</t>
+          <t>ball_possession_away</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ball_possession_home</t>
+          <t>goal_attempts_home</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>ball_possession_away</t>
+          <t>goal_attempts_away</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>goal_attempts_home</t>
+          <t>shots_on_goal_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>goal_attempts_away</t>
+          <t>shots_on_goal_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>shots_on_goal_home</t>
+          <t>fouls_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>shots_on_goal_away</t>
+          <t>fouls_away</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>fouls_home</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>fouls_away</t>
+          <t>id_coach_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_home</t>
+          <t>id_country</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>id_coach_away</t>
+          <t>id_competition</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>id_country</t>
+          <t>is_cup</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>id_competition</t>
+          <t>season</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>is_cup</t>
+          <t>id_team_home_rival_team</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>season</t>
+          <t>id_team_away_rival_team</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_sub_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_sub_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_sub_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_sub_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_sub_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_sub_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
@@ -692,839 +682,581 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IViLLjPF</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45523.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">merkur spiel arena
-  dusseldorf </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>54600</v>
-      </c>
-      <c r="F2" t="n">
-        <v>36103</v>
-      </c>
+        <v>23325</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1.09</v>
+        <v>41</v>
       </c>
       <c r="L2" t="n">
-        <v>0.66</v>
+        <v>59</v>
       </c>
       <c r="M2" t="n">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="N2" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="O2" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R2" t="n">
         <v>6</v>
       </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>OzPMRhK3</t>
-        </is>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="U2" t="n">
+        <v>59</v>
+      </c>
+      <c r="V2" t="n">
+        <v>593</v>
       </c>
       <c r="W2" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>185.625</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.63636363636364</v>
+        <v>1.125</v>
       </c>
       <c r="AD2" t="n">
-        <v>182.7272727272727</v>
+        <v>67.625</v>
       </c>
       <c r="AE2" t="n">
+        <v>1325000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>70.625</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>184.3333333333333</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>76.88888888888889</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>14777777.77777778</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>82</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>181.5333333333333</v>
+      </c>
+      <c r="AO2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2334090.909090909</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>73.90909090909091</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>26.27272727272727</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>184.3636363636364</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>67.81818181818181</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1395454.545454545</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>71.90909090909091</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>22.69230769230769</v>
-      </c>
       <c r="AP2" t="n">
-        <v>186.3846153846154</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>1386666.666666667</v>
       </c>
       <c r="AR2" t="n">
-        <v>66</v>
+        <v>71.73333333333333</v>
       </c>
       <c r="AS2" t="n">
-        <v>1753846.153846154</v>
+        <v>20.31578947368421</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.53846153846153</v>
+        <v>185.3684210526316</v>
       </c>
       <c r="AU2" t="n">
-        <v>23.3125</v>
+        <v>1.315789473684211</v>
       </c>
       <c r="AV2" t="n">
-        <v>181</v>
+        <v>70.31578947368421</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>6257894.736842105</v>
       </c>
       <c r="AX2" t="n">
-        <v>65.25</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1126250</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>72.5625</v>
+        <v>80.94736842105263</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tC1Aa08D</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bauer t 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">waldstadion kaiserlinde
-  spiesen elversberg </t>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9970</v>
-      </c>
-      <c r="F3" t="n">
-        <v>9502</v>
-      </c>
+        <v>22450</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.45</v>
+        <v>39</v>
       </c>
       <c r="L3" t="n">
-        <v>3.39</v>
+        <v>61</v>
       </c>
       <c r="M3" t="n">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="R3" t="n">
         <v>9</v>
       </c>
-      <c r="S3" t="n">
-        <v>13</v>
-      </c>
-      <c r="T3" t="n">
-        <v>13</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>8E8qmw3d</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>4fX0k7gg</t>
-        </is>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>tnTvQd1l</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>59</v>
+      </c>
+      <c r="V3" t="n">
+        <v>593</v>
       </c>
       <c r="W3" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
         <v>20242025</v>
       </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>182.3</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>66.90000000000001</v>
-      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>1200000</v>
+        <v>25.45454545454545</v>
       </c>
       <c r="AH3" t="n">
-        <v>70.5</v>
+        <v>184.2727272727273</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AJ3" t="n">
-        <v>185.4545454545455</v>
+        <v>73.27272727272727</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.181818181818182</v>
+        <v>5290909.090909091</v>
       </c>
       <c r="AL3" t="n">
-        <v>71.27272727272727</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>4545454.545454546</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>78.63636363636364</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>25.30769230769231</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>182.3076923076923</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>65.23076923076923</v>
-      </c>
+        <v>76.90909090909091</v>
+      </c>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>975000</v>
+        <v>25.58823529411765</v>
       </c>
       <c r="AT3" t="n">
-        <v>69.07692307692308</v>
+        <v>183.0588235294118</v>
       </c>
       <c r="AU3" t="n">
-        <v>26.33333333333333</v>
+        <v>1.235294117647059</v>
       </c>
       <c r="AV3" t="n">
-        <v>186.5714285714286</v>
+        <v>71.29411764705883</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.380952380952381</v>
+        <v>3341176.470588235</v>
       </c>
       <c r="AX3" t="n">
-        <v>69.47619047619048</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>2787619.047619048</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>73.19047619047619</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>YJ3eN30K</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45514.33333333334</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">winter n 
+          <t xml:space="preserve">alt p 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">max morlock stadion
-  nuremberg </t>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>44308</v>
-      </c>
-      <c r="F4" t="n">
-        <v>50000</v>
-      </c>
+        <v>20500</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.93</v>
+        <v>26</v>
       </c>
       <c r="L4" t="n">
-        <v>2.12</v>
+        <v>74</v>
       </c>
       <c r="M4" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>11</v>
-      </c>
-      <c r="T4" t="n">
-        <v>12</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
+        <v>20</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>GWkh67yH</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>59</v>
+      </c>
+      <c r="V4" t="n">
+        <v>593</v>
       </c>
       <c r="W4" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="AC4" t="n">
-        <v>22.77777777777778</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>182</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>66</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1697222.222222222</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>72.55555555555556</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>25.625</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>189.75</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="n">
+        <v>25.31578947368421</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>178.578947368421</v>
+      </c>
+      <c r="AU4" t="n">
         <v>1</v>
       </c>
-      <c r="AL4" t="n">
-        <v>67.625</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1540625</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>28.125</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>180</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>67.875</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1209375</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>26.57142857142857</v>
-      </c>
       <c r="AV4" t="n">
-        <v>186.7142857142857</v>
+        <v>66.68421052631579</v>
       </c>
       <c r="AW4" t="n">
-        <v>1</v>
+        <v>1192105.263157895</v>
       </c>
       <c r="AX4" t="n">
-        <v>68.57142857142857</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1428571.428571429</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>70.57142857142857</v>
+        <v>69.10526315789474</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>h4pSHsOs</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">lechner f 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz walter stadion
-  kaiserslautern </t>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>49500</v>
-      </c>
-      <c r="F5" t="n">
-        <v>41632</v>
-      </c>
+        <v>9500</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>p8wBsqZt</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>24</v>
+      </c>
+      <c r="L5" t="n">
+        <v>76</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>18</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M5" t="n">
-        <v>54</v>
-      </c>
-      <c r="N5" t="n">
-        <v>46</v>
-      </c>
-      <c r="O5" t="n">
-        <v>13</v>
-      </c>
-      <c r="P5" t="n">
-        <v>15</v>
-      </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="R5" t="n">
-        <v>8</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="n">
-        <v>14</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>4bJLk19p</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>8E86CPuD</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>rFNN7oyi</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>59</v>
+      </c>
+      <c r="V5" t="n">
+        <v>593</v>
       </c>
       <c r="W5" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
         <v>20242025</v>
       </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>25</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>184.6363636363636</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>67.63636363636364</v>
-      </c>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>1484090.909090909</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AH5" t="n">
-        <v>70.63636363636364</v>
+        <v>185.8888888888889</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AJ5" t="n">
-        <v>183.1</v>
+        <v>76</v>
       </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>12611111.11111111</v>
       </c>
       <c r="AL5" t="n">
-        <v>67</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1480000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>25.23529411764706</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>181.4705882352941</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>68.05882352941177</v>
-      </c>
+        <v>80.55555555555556</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
       <c r="AS5" t="n">
-        <v>1691176.470588235</v>
+        <v>22.08333333333333</v>
       </c>
       <c r="AT5" t="n">
-        <v>71.29411764705883</v>
+        <v>186.3333333333333</v>
       </c>
       <c r="AU5" t="n">
-        <v>23.13636363636364</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="AV5" t="n">
-        <v>183.8181818181818</v>
+        <v>71.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>6483333.333333333</v>
       </c>
       <c r="AX5" t="n">
-        <v>65.31818181818181</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1430681.818181818</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>73.09090909090909</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>StuiCwhJ</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45513.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">benen l 
-  ger </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>15210</v>
-      </c>
-      <c r="F6" t="n">
-        <v>12095</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>tbC3EcQn</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="M6" t="n">
-        <v>49</v>
-      </c>
-      <c r="N6" t="n">
-        <v>51</v>
-      </c>
-      <c r="O6" t="n">
-        <v>8</v>
-      </c>
-      <c r="P6" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>22</v>
-      </c>
-      <c r="T6" t="n">
-        <v>16</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>zyLSrbZQ</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>59</v>
-      </c>
-      <c r="X6" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>183</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>62</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>887500</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>70.5</v>
+        <v>79.16666666666667</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:BN13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,784 +480,2702 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>ball_possession_home</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ball_possession_away</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_home</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>goal_attempts_away</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>shots_on_goal_away</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>fouls_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fouls_away</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>id_team_home_rival_team</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">eintracht stadion
-  braunschweig </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23325</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>81365</v>
+      </c>
+      <c r="F2" t="n">
+        <v>81365</v>
+      </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>59</v>
+      </c>
+      <c r="X2" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>185.8</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>38400000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>184.875</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>77.375</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>15812500</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>82.125</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>23.1304347826087</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>184.8260869565217</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.695652173913043</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>77.43478260869566</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>20739130.43478261</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>83.21739130434783</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>20.68421052631579</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>185.1578947368421</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.315789473684211</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>71.15789473684211</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7373684.210526315</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>81.15789473684211</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>41</v>
-      </c>
-      <c r="L2" t="n">
-        <v>59</v>
-      </c>
-      <c r="M2" t="n">
-        <v>7</v>
-      </c>
-      <c r="N2" t="n">
-        <v>14</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="BE2" t="n">
+        <v>81</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>81</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>19</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>180</v>
+      </c>
+      <c r="BJ2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>SQrxFAMl</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="U2" t="n">
-        <v>59</v>
-      </c>
-      <c r="V2" t="n">
-        <v>593</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>26.375</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>185.625</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>67.625</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1325000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>70.625</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>23.77777777777778</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>184.3333333333333</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>76.88888888888889</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>14777777.77777778</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>82</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>181.5333333333333</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1386666.666666667</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>71.73333333333333</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>20.31578947368421</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>185.3684210526316</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.315789473684211</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>70.31578947368421</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6257894.736842105</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>80.94736842105263</v>
+      <c r="BK2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>121</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion der freundschaft
-  cottbus </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22450</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>30660</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30660</v>
+      </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M3" t="n">
+        <v>45</v>
+      </c>
+      <c r="N3" t="n">
+        <v>55</v>
+      </c>
+      <c r="O3" t="n">
+        <v>10</v>
+      </c>
+      <c r="P3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>11</v>
+      </c>
+      <c r="T3" t="n">
+        <v>10</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>59</v>
+      </c>
+      <c r="X3" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>24.625</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>185.125</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>4975000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>25.45454545454545</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>184.2727272727273</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>73.27272727272727</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>5290909.090909091</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>76.90909090909091</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>23.9375</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>183.25</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4801562.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>76.9375</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>25.23529411764706</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>184.8235294117647</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.235294117647059</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>71.05882352941177</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3376470.588235294</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>76.35294117647059</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="BC3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6g44VD52</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>39</v>
-      </c>
-      <c r="L3" t="n">
-        <v>61</v>
-      </c>
-      <c r="M3" t="n">
-        <v>8</v>
-      </c>
-      <c r="N3" t="n">
-        <v>18</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>13</v>
-      </c>
-      <c r="R3" t="n">
-        <v>9</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>tnTvQd1l</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>59</v>
-      </c>
-      <c r="V3" t="n">
-        <v>593</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
-        <v>25.45454545454545</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>184.2727272727273</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>73.27272727272727</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>5290909.090909091</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>76.90909090909091</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>25.58823529411765</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>183.0588235294118</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.235294117647059</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>71.29411764705883</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>3341176.470588235</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>76</v>
+      <c r="BD3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>362</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>19900000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>373</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>150</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">alt p 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">bieberer berg stadion
-  offenbach am main </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>34700</v>
+      </c>
+      <c r="F4" t="n">
+        <v>34700</v>
+      </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>YJURlaIO</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>26</v>
+        <v>2.66</v>
       </c>
       <c r="L4" t="n">
-        <v>74</v>
+        <v>0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="N4" t="n">
+        <v>64</v>
+      </c>
+      <c r="O4" t="n">
         <v>15</v>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
       </c>
       <c r="P4" t="n">
         <v>9</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>20</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>GWkh67yH</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>IgZoGKFn</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
         <v>59</v>
       </c>
-      <c r="V4" t="n">
-        <v>593</v>
-      </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>184</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>9550000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>24.33333333333333</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.222222222222222</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>75.33333333333333</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>10344444.44444444</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>78.55555555555556</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>26.47619047619047</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>182.2857142857143</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.80952380952381</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>75.42857142857143</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10057142.85714286</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>76.95238095238095</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>22.55555555555556</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>185.4444444444445</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>69.16666666666667</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4505555.555555556</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>76.94444444444444</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>24</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="BC4" t="n">
         <v>1</v>
       </c>
-      <c r="X4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="n">
-        <v>25.31578947368421</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>178.578947368421</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>66.68421052631579</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1192105.263157895</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>69.10526315789474</v>
+      <c r="BD4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>429</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>26800000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>458</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>22.28571428571428</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>188.7142857142857</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>495</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>36825000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>541</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion oberwerth
-  koblenz </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>30150</v>
+      </c>
+      <c r="F5" t="n">
+        <v>18503</v>
+      </c>
       <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="M5" t="n">
+        <v>53</v>
+      </c>
+      <c r="N5" t="n">
+        <v>47</v>
+      </c>
+      <c r="O5" t="n">
+        <v>20</v>
+      </c>
+      <c r="P5" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>59</v>
+      </c>
+      <c r="X5" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="n">
+      <c r="Z5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>9135000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>25.22222222222222</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>186.2222222222222</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1666666.666666667</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>72.22222222222223</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>185.6111111111111</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>72.33333333333333</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8165277.777777778</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>79</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>25.38888888888889</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>184.3888888888889</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.055555555555556</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>67.94444444444444</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1684722.222222222</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>71.77777777777777</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>180.8571428571429</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.285714285714286</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>501</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>32700000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>565</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>184</v>
+      </c>
+      <c r="BJ5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>p8wBsqZt</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="BK5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>207</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>5750000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>31500</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M6" t="n">
+        <v>53</v>
+      </c>
+      <c r="N6" t="n">
+        <v>47</v>
+      </c>
+      <c r="O6" t="n">
+        <v>15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
+      <c r="S6" t="n">
+        <v>9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>15</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>59</v>
+      </c>
+      <c r="X6" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>8170000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>78</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>23.55555555555556</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>183.9444444444445</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>70.05555555555556</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2845833.333333333</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>78</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>25.52380952380953</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>183.4285714285714</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>72.66666666666667</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>4226190.476190476</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>76.19047619047619</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="n">
+        <v>29</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>175.6666666666667</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>229</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>25300000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45528.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F7" t="n">
+        <v>44611</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>59</v>
+      </c>
+      <c r="N7" t="n">
+        <v>41</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>9</v>
+      </c>
+      <c r="T7" t="n">
+        <v>17</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>59</v>
+      </c>
+      <c r="X7" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>24.81818181818182</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>182.8181818181818</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>2.090909090909091</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>79.72727272727273</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>27409090.90909091</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>83.81818181818181</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>183.125</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>71.375</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>2340625</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>73.875</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>25.05555555555556</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>184.8333333333333</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.888888888888889</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>78.88888888888889</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>22611111.11111111</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>81.94444444444444</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>22.13333333333333</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>185.4666666666667</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>66.06666666666666</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1545000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>214</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>33400000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>250</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>282</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>8250000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45527.64583333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F8" t="n">
+        <v>54042</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>46</v>
+      </c>
+      <c r="N8" t="n">
+        <v>54</v>
+      </c>
+      <c r="O8" t="n">
+        <v>14</v>
+      </c>
+      <c r="P8" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>9</v>
+      </c>
+      <c r="S8" t="n">
+        <v>11</v>
+      </c>
+      <c r="T8" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>59</v>
+      </c>
+      <c r="X8" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC8" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>184.2727272727273</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.636363636363636</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>76.45454545454545</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>78.54545454545455</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>184.4</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>24.16666666666667</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>184.4583333333333</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>77.54166666666667</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>23.77777777777778</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>182.5555555555555</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>77.11111111111111</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>22177777.77777778</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>82.33333333333333</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>194</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4625000</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>230</v>
+      </c>
+      <c r="BH8" t="n">
         <v>24</v>
       </c>
-      <c r="L5" t="n">
-        <v>76</v>
-      </c>
-      <c r="M5" t="n">
+      <c r="BI8" t="n">
+        <v>178</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>81</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>36500000</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>S2GROGyP</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45528.33333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">braun r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sportpark ronhof thomas sommer
+  furth </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>16626</v>
+      </c>
+      <c r="F9" t="n">
+        <v>10261</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M9" t="n">
+        <v>52</v>
+      </c>
+      <c r="N9" t="n">
+        <v>48</v>
+      </c>
+      <c r="O9" t="n">
+        <v>14</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12</v>
+      </c>
+      <c r="T9" t="n">
+        <v>16</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>8E86CPuD</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0AI1QUJH</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>59</v>
+      </c>
+      <c r="X9" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>67</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1480000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>183.375</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>66.625</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1384375</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>72.625</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1551250</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>73.45</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>67.6875</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1481250</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>71.9375</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>IReyqKMt</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45528.33333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hempel r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">olympiastadion
+  berlin </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>74667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42355</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>UiCmEP56</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M10" t="n">
+        <v>67</v>
+      </c>
+      <c r="N10" t="n">
+        <v>33</v>
+      </c>
+      <c r="O10" t="n">
+        <v>11</v>
+      </c>
+      <c r="P10" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>59</v>
+      </c>
+      <c r="X10" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>183</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2380000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>184.45</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2368750</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lGJRqVt2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45528.33333333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bacher m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12794</v>
+      </c>
+      <c r="F11" t="n">
+        <v>12422</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="M11" t="n">
+        <v>43</v>
+      </c>
+      <c r="N11" t="n">
+        <v>57</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="n">
+        <v>18</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>59</v>
+      </c>
+      <c r="X11" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1602500</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>66</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1269444.444444444</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>25.31818181818182</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>182.2272727272727</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>67.77272727272727</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1555681.818181818</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>70.90909090909091</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>800QQx7C</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45527.5625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alt p 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heinz von heiden arena
+  hannover </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>49200</v>
+      </c>
+      <c r="F12" t="n">
+        <v>49000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M12" t="n">
+        <v>52</v>
+      </c>
+      <c r="N12" t="n">
+        <v>48</v>
+      </c>
+      <c r="O12" t="n">
+        <v>9</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="n">
+        <v>18</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>59</v>
+      </c>
+      <c r="X12" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.181818181818182</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>70.27272727272727</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2138636.363636364</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>25.44444444444444</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>184.6666666666667</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>71.66666666666667</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>2911111.111111111</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>74.77777777777777</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>68.25</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1988750</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>74.15000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>26.84615384615385</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>186.6923076923077</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>70.15384615384616</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>2513846.153846154</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>71.92307692307692</v>
+      </c>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>zm2ISbx0</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45527.5625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prigan f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bbbank wildpark
+  karlsruhe </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>34302</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26838</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>50</v>
+      </c>
+      <c r="N13" t="n">
+        <v>50</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3</v>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+      <c r="T13" t="n">
         <v>6</v>
       </c>
-      <c r="N5" t="n">
-        <v>18</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>59</v>
+      </c>
+      <c r="X13" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="n">
+        <v>26.27272727272727</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>184.3636363636364</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>19</v>
-      </c>
-      <c r="R5" t="n">
-        <v>9</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>rFNN7oyi</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>59</v>
-      </c>
-      <c r="V5" t="n">
-        <v>593</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AF13" t="n">
+        <v>67.81818181818181</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1395454.545454545</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1</v>
       </c>
-      <c r="X5" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
-        <v>24.11111111111111</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>185.8888888888889</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>76</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>12611111.11111111</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>80.55555555555556</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="n">
-        <v>22.08333333333333</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.166666666666667</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>71.75</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6483333.333333333</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>79.16666666666667</v>
-      </c>
+      <c r="AL13" t="n">
+        <v>66.09090909090909</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1179545.454545455</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>23.73333333333333</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>182.8666666666667</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1133000</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>72.13333333333334</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>184</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>66.33333333333333</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1441666.666666667</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>72</v>
+      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN7"/>
+  <dimension ref="A1:BN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,84 +762,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F2" t="n">
-        <v>29157</v>
-      </c>
+        <v>22012</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>43</v>
+      </c>
+      <c r="N2" t="n">
+        <v>57</v>
+      </c>
+      <c r="O2" t="n">
+        <v>10</v>
+      </c>
+      <c r="P2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
         <v>2</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M2" t="n">
-        <v>58</v>
-      </c>
-      <c r="N2" t="n">
-        <v>42</v>
-      </c>
-      <c r="O2" t="n">
-        <v>11</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -854,215 +852,213 @@
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
         <v>25.6</v>
       </c>
       <c r="AD2" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>7560000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>185.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2210000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>26.375</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>188.125</v>
       </c>
       <c r="AK2" t="n">
         <v>1</v>
       </c>
       <c r="AL2" t="n">
-        <v>72.125</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
-        <v>2800000</v>
+        <v>2210000</v>
       </c>
       <c r="AN2" t="n">
-        <v>74.125</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>24.05882352941176</v>
+        <v>24.85</v>
       </c>
       <c r="AP2" t="n">
-        <v>182.3529411764706</v>
+        <v>181.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>69.41176470588235</v>
+        <v>71.95</v>
       </c>
       <c r="AS2" t="n">
-        <v>2294117.647058824</v>
+        <v>3627500</v>
       </c>
       <c r="AT2" t="n">
-        <v>73.76470588235294</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>25.55555555555556</v>
+        <v>25.21052631578947</v>
       </c>
       <c r="AV2" t="n">
-        <v>185.1111111111111</v>
+        <v>185.2105263157895</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
       </c>
       <c r="AX2" t="n">
-        <v>69.61111111111111</v>
+        <v>68.78947368421052</v>
       </c>
       <c r="AY2" t="n">
-        <v>1869444.444444444</v>
+        <v>1969736.842105263</v>
       </c>
       <c r="AZ2" t="n">
-        <v>71.94444444444444</v>
+        <v>73.10526315789474</v>
       </c>
       <c r="BA2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BB2" t="n">
-        <v>186.6666666666667</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BD2" t="n">
         <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>199</v>
+        <v>223</v>
       </c>
       <c r="BF2" t="n">
-        <v>2575000</v>
+        <v>22100000</v>
       </c>
       <c r="BG2" t="n">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="BH2" t="n">
-        <v>22.5</v>
+        <v>30</v>
       </c>
       <c r="BI2" t="n">
-        <v>190.5</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="BJ2" t="n">
         <v>1</v>
       </c>
       <c r="BK2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL2" t="n">
-        <v>134</v>
+        <v>199</v>
       </c>
       <c r="BM2" t="n">
-        <v>3400000</v>
+        <v>2575000</v>
       </c>
       <c r="BN2" t="n">
-        <v>145</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>SGe0wGjI</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.4375</v>
+        <v>45534.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">merkur spiel arena
+  dusseldorf </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28917</v>
-      </c>
-      <c r="F3" t="n">
-        <v>28917</v>
-      </c>
+        <v>54600</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="L3" t="n">
-        <v>2.85</v>
+        <v>0.7</v>
       </c>
       <c r="M3" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="N3" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="O3" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="P3" t="n">
         <v>14</v>
       </c>
       <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
         <v>2</v>
       </c>
-      <c r="R3" t="n">
-        <v>8</v>
-      </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T3" t="n">
         <v>11</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>59</v>
       </c>
       <c r="X3" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1072,206 +1068,180 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
       <c r="AC3" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1817500</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1902500</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>22.15789473684211</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>186.3157894736842</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>65.94736842105263</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1517105.263157895</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>75.68421052631579</v>
+      </c>
+      <c r="AU3" t="n">
         <v>24</v>
       </c>
-      <c r="AD3" t="n">
-        <v>184.375</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11087500</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>79.875</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>83</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>53820000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>86.59999999999999</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>185.2</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>75.40000000000001</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10653333.33333333</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>78.26666666666667</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>28.125</v>
-      </c>
       <c r="AV3" t="n">
-        <v>184</v>
+        <v>182.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.875</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="n">
-        <v>81.125</v>
+        <v>67.25</v>
       </c>
       <c r="AY3" t="n">
-        <v>29639062.5</v>
+        <v>1571250</v>
       </c>
       <c r="AZ3" t="n">
-        <v>82.4375</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>183.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>375</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>48500000</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>403</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>21.83333333333333</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>184.8333333333333</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>430</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>98525000</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>489</v>
-      </c>
+        <v>72.5</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vL89UK7m</t>
+          <t>vs08wy8F</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.35416666666</v>
+        <v>45534.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">schwengers p 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">merck stadion am bollenfalltor
-  darmstadt </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>17810</v>
-      </c>
-      <c r="F4" t="n">
-        <v>17600</v>
-      </c>
+        <v>15210</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="L4" t="n">
-        <v>0.37</v>
+        <v>2.23</v>
       </c>
       <c r="M4" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="N4" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="Q4" t="n">
         <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -1286,14 +1256,10 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1303,58 +1269,46 @@
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>23.25</v>
+        <v>24.63636363636364</v>
       </c>
       <c r="AJ4" t="n">
-        <v>183.5</v>
+        <v>183.6363636363636</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.125</v>
+        <v>1</v>
       </c>
       <c r="AL4" t="n">
-        <v>67.75</v>
+        <v>67</v>
       </c>
       <c r="AM4" t="n">
-        <v>2181250</v>
+        <v>1536363.636363636</v>
       </c>
       <c r="AN4" t="n">
-        <v>74.125</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>25.72222222222222</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>188.5555555555555</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>68.44444444444444</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1594444.444444444</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>73.11111111111111</v>
-      </c>
+        <v>71.90909090909091</v>
+      </c>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>25</v>
+        <v>23.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>175.8</v>
+        <v>182.55</v>
       </c>
       <c r="AW4" t="n">
         <v>1</v>
       </c>
       <c r="AX4" t="n">
-        <v>68.3</v>
+        <v>65.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1635000</v>
+        <v>1471250</v>
       </c>
       <c r="AZ4" t="n">
-        <v>70.40000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
@@ -1374,94 +1328,90 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vsppsbig</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.35416666666</v>
+        <v>45532.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mdcc arena
-  magdeburg </t>
+          <t xml:space="preserve">ernst abbe sportfeld
+  jena </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30098</v>
+        <v>10445</v>
       </c>
       <c r="F5" t="n">
-        <v>27146</v>
+        <v>15000</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>APNl8MIn</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.22</v>
-      </c>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="N5" t="n">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="n">
         <v>14</v>
       </c>
-      <c r="P5" t="n">
-        <v>13</v>
-      </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>IgZoGKFn</t>
+          <t>WzqXh8OL</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>txZLBQVC</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>59</v>
       </c>
       <c r="X5" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
         <v>20242025</v>
@@ -1469,68 +1419,44 @@
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="AC5" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>180.875</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>67.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1356250</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>70.5</v>
-      </c>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="n">
-        <v>24.4375</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>179.8125</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>66.75</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>1339062.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>69.75</v>
-      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>27.2</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="AV5" t="n">
-        <v>182.9</v>
+        <v>178</v>
       </c>
       <c r="AW5" t="n">
-        <v>1</v>
+        <v>2.277777777777778</v>
       </c>
       <c r="AX5" t="n">
-        <v>69.5</v>
+        <v>81.44444444444444</v>
       </c>
       <c r="AY5" t="n">
-        <v>1650000</v>
+        <v>51204166.66666666</v>
       </c>
       <c r="AZ5" t="n">
-        <v>70.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
@@ -1550,94 +1476,90 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>n7mhuxM5</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45529.35416666666</v>
+        <v>45531.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">weisbach e 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">preussenstadion
+  munster </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19500</v>
+        <v>12794</v>
       </c>
       <c r="F6" t="n">
-        <v>13226</v>
+        <v>12672</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3.87</v>
-      </c>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="N6" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="O6" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" t="n">
         <v>12</v>
       </c>
-      <c r="Q6" t="n">
-        <v>8</v>
-      </c>
-      <c r="R6" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
       <c r="T6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>59</v>
       </c>
       <c r="X6" t="n">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>20242025</v>
@@ -1645,7 +1567,7 @@
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1655,46 +1577,58 @@
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="n">
-        <v>26.18181818181818</v>
+        <v>24.11111111111111</v>
       </c>
       <c r="AJ6" t="n">
-        <v>184.6363636363636</v>
+        <v>188.4444444444445</v>
       </c>
       <c r="AK6" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>72.88888888888889</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>8088888.888888889</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>77</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>25.14285714285714</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ6" t="n">
         <v>1</v>
       </c>
-      <c r="AL6" t="n">
-        <v>70.45454545454545</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>2181818.181818182</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>73.18181818181819</v>
-      </c>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
+      <c r="AR6" t="n">
+        <v>66.28571428571429</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1228571.428571429</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>69.57142857142857</v>
+      </c>
       <c r="AU6" t="n">
-        <v>22.28571428571428</v>
+        <v>23.1875</v>
       </c>
       <c r="AV6" t="n">
-        <v>185.7142857142857</v>
+        <v>181.3125</v>
       </c>
       <c r="AW6" t="n">
-        <v>1</v>
+        <v>1.125</v>
       </c>
       <c r="AX6" t="n">
-        <v>65.80952380952381</v>
+        <v>72.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>1441666.666666667</v>
+        <v>7993750</v>
       </c>
       <c r="AZ6" t="n">
-        <v>75.23809523809524</v>
+        <v>79.25</v>
       </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
@@ -1711,198 +1645,6 @@
       <c r="BM6" t="inlineStr"/>
       <c r="BN6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>8xIwzspQ</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rheinenergiestadion
-  cologne </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F7" t="n">
-        <v>50000</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M7" t="n">
-        <v>29</v>
-      </c>
-      <c r="N7" t="n">
-        <v>71</v>
-      </c>
-      <c r="O7" t="n">
-        <v>22</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>13</v>
-      </c>
-      <c r="R7" t="n">
-        <v>3</v>
-      </c>
-      <c r="S7" t="n">
-        <v>14</v>
-      </c>
-      <c r="T7" t="n">
-        <v>7</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>4fX0k7gg</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>SQrxFAMl</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>59</v>
-      </c>
-      <c r="X7" t="n">
-        <v>592</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="AC7" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>185.2</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>71.3</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>4840000</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>79.40000000000001</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>26.375</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>185.625</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>67.625</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1325000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>70.625</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>24.89473684210526</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>187</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.263157894736842</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>69.47368421052632</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3494736.842105263</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>74.26315789473684</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>22.61538461538462</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>181.7692307692308</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>65.76923076923077</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1417307.692307692</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>73.84615384615384</v>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
-      <c r="BI7" t="inlineStr"/>
-      <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="inlineStr"/>
-      <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN6"/>
+  <dimension ref="A1:BN11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -762,82 +762,84 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45535.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22012</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>30210</v>
+      </c>
+      <c r="F2" t="n">
+        <v>28000</v>
+      </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.8</v>
+        <v>2.93</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="N2" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="O2" t="n">
+        <v>27</v>
+      </c>
+      <c r="P2" t="n">
         <v>10</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T2" t="n">
         <v>8</v>
       </c>
-      <c r="Q2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>10</v>
-      </c>
-      <c r="T2" t="n">
-        <v>11</v>
-      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="W2" t="n">
@@ -852,213 +854,219 @@
       <c r="Z2" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="AC2" t="n">
-        <v>25.6</v>
+        <v>24.125</v>
       </c>
       <c r="AD2" t="n">
-        <v>186.9</v>
+        <v>183.25</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AG2" t="n">
-        <v>7560000</v>
+        <v>51625000</v>
       </c>
       <c r="AH2" t="n">
-        <v>78.5</v>
+        <v>86.375</v>
       </c>
       <c r="AI2" t="n">
-        <v>25.6</v>
+        <v>24.45454545454545</v>
       </c>
       <c r="AJ2" t="n">
-        <v>185.5</v>
+        <v>184.2727272727273</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>78.63636363636364</v>
       </c>
       <c r="AM2" t="n">
-        <v>2210000</v>
+        <v>24372727.27272727</v>
       </c>
       <c r="AN2" t="n">
-        <v>73.59999999999999</v>
+        <v>83.09090909090909</v>
       </c>
       <c r="AO2" t="n">
-        <v>24.85</v>
+        <v>24.29411764705882</v>
       </c>
       <c r="AP2" t="n">
-        <v>181.5</v>
+        <v>183</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.2</v>
+        <v>1.529411764705882</v>
       </c>
       <c r="AR2" t="n">
-        <v>71.95</v>
+        <v>75.70588235294117</v>
       </c>
       <c r="AS2" t="n">
-        <v>3627500</v>
+        <v>20316176.47058824</v>
       </c>
       <c r="AT2" t="n">
-        <v>76.09999999999999</v>
+        <v>80.23529411764706</v>
       </c>
       <c r="AU2" t="n">
-        <v>25.21052631578947</v>
+        <v>24.73333333333333</v>
       </c>
       <c r="AV2" t="n">
-        <v>185.2105263157895</v>
+        <v>182.8666666666667</v>
       </c>
       <c r="AW2" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>68.78947368421052</v>
+        <v>78.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>1969736.842105263</v>
+        <v>21700000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>73.10526315789474</v>
+        <v>82.26666666666667</v>
       </c>
       <c r="BA2" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>180.3333333333333</v>
+        <v>185</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.333333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BE2" t="n">
-        <v>223</v>
+        <v>163</v>
       </c>
       <c r="BF2" t="n">
-        <v>22100000</v>
+        <v>46500000</v>
       </c>
       <c r="BG2" t="n">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="BH2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BI2" t="n">
-        <v>186.6666666666667</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK2" t="n">
         <v>3</v>
       </c>
       <c r="BL2" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="BM2" t="n">
-        <v>2575000</v>
+        <v>60800000</v>
       </c>
       <c r="BN2" t="n">
-        <v>204</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SGe0wGjI</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">merkur spiel arena
-  dusseldorf </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>54600</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>26000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>26000</v>
+      </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.07</v>
+        <v>1.07</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7</v>
+        <v>2.84</v>
       </c>
       <c r="M3" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="N3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="O3" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>t0ZPdkUl</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="W3" t="n">
         <v>59</v>
       </c>
       <c r="X3" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -1068,187 +1076,205 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="AC3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>184.1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>69.5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1817500</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>72.5</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>25.3</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="AJ3" t="n">
-        <v>182.7</v>
+        <v>185.0909090909091</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.1</v>
+        <v>1.636363636363636</v>
       </c>
       <c r="AL3" t="n">
-        <v>69.5</v>
+        <v>76.18181818181819</v>
       </c>
       <c r="AM3" t="n">
-        <v>1902500</v>
+        <v>10145454.54545454</v>
       </c>
       <c r="AN3" t="n">
-        <v>73.5</v>
+        <v>77.90909090909091</v>
       </c>
       <c r="AO3" t="n">
-        <v>22.15789473684211</v>
+        <v>22.85714285714286</v>
       </c>
       <c r="AP3" t="n">
-        <v>186.3157894736842</v>
+        <v>186.2142857142857</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>65.94736842105263</v>
+        <v>67</v>
       </c>
       <c r="AS3" t="n">
-        <v>1517105.263157895</v>
+        <v>1676785.714285714</v>
       </c>
       <c r="AT3" t="n">
-        <v>75.68421052631579</v>
+        <v>75.78571428571429</v>
       </c>
       <c r="AU3" t="n">
-        <v>24</v>
+        <v>24.33333333333333</v>
       </c>
       <c r="AV3" t="n">
-        <v>182.2</v>
+        <v>183.0416666666667</v>
       </c>
       <c r="AW3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>73.58333333333333</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>6058333.333333333</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>77.625</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>282</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>8250000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>295</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>19.33333333333333</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>1</v>
       </c>
-      <c r="AX3" t="n">
-        <v>67.25</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1571250</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="inlineStr"/>
+      <c r="BK3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>194</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>4625000</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>230</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vs08wy8F</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">schwengers p 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>15210</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>58000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>57100</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>2.23</v>
+        <v>1.29</v>
       </c>
       <c r="M4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="N4" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
         <v>17</v>
       </c>
       <c r="P4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Q4" t="n">
         <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>8E86CPuD</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="W4" t="n">
         <v>59</v>
       </c>
       <c r="X4" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -1256,394 +1282,1512 @@
       <c r="Z4" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14562500</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>81.5</v>
+      </c>
       <c r="AI4" t="n">
-        <v>24.63636363636364</v>
+        <v>26.9</v>
       </c>
       <c r="AJ4" t="n">
-        <v>183.6363636363636</v>
+        <v>185.1</v>
       </c>
       <c r="AK4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>9135000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>20.45454545454545</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>185.9545454545455</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.318181818181818</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>70.90909090909091</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7818181.818181818</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>81.45454545454545</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>25.84615384615385</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>186.7692307692308</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.461538461538461</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>72.69230769230769</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>7503846.153846154</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>76.38461538461539</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>180</v>
+      </c>
+      <c r="BC4" t="n">
         <v>1</v>
       </c>
-      <c r="AL4" t="n">
-        <v>67</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1536363.636363636</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>71.90909090909091</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>182.55</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1471250</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>73.15000000000001</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+      <c r="BD4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>121</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>159</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>181.8333333333333</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>433</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>29600000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>481</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6u6i5pie</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45532.54166666666</v>
+        <v>45535.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ernst abbe sportfeld
-  jena </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>10445</v>
+        <v>15034</v>
       </c>
       <c r="F5" t="n">
-        <v>15000</v>
+        <v>15034</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>APNl8MIn</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.38</v>
+      </c>
       <c r="M5" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="N5" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>5</v>
+      </c>
+      <c r="R5" t="n">
         <v>4</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
+        <v>17</v>
+      </c>
+      <c r="T5" t="n">
         <v>14</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7</v>
-      </c>
-      <c r="S5" t="n">
-        <v>16</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>WzqXh8OL</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="W5" t="n">
         <v>59</v>
       </c>
       <c r="X5" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>185.6666666666667</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>68.55555555555556</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1483333.333333333</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>70.77777777777777</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>184.375</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>11087500</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>79.875</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>24.17647058823529</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>185.7058823529412</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.058823529411765</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>67</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1672058.823529412</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>72.35294117647059</v>
+      </c>
       <c r="AU5" t="n">
-        <v>24.66666666666667</v>
+        <v>24.6875</v>
       </c>
       <c r="AV5" t="n">
-        <v>178</v>
+        <v>185.75</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.277777777777778</v>
+        <v>1.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>81.44444444444444</v>
+        <v>74.5625</v>
       </c>
       <c r="AY5" t="n">
-        <v>51204166.66666666</v>
+        <v>10631250</v>
       </c>
       <c r="AZ5" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>79.125</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>25</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>149</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>182</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>300</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>41500000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>324</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>W67CmLPh</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45531.65625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">preussenstadion
-  munster </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12794</v>
+        <v>60449</v>
       </c>
       <c r="F6" t="n">
-        <v>12672</v>
+        <v>59000</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>zedZaSL7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.25</v>
+      </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="N6" t="n">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="P6" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q6" t="n">
         <v>13</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T6" t="n">
         <v>12</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="W6" t="n">
         <v>59</v>
       </c>
       <c r="X6" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>8610000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>77.7</v>
+      </c>
       <c r="AI6" t="n">
-        <v>24.11111111111111</v>
+        <v>27.44444444444444</v>
       </c>
       <c r="AJ6" t="n">
-        <v>188.4444444444445</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.333333333333333</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AL6" t="n">
-        <v>72.88888888888889</v>
+        <v>74.88888888888889</v>
       </c>
       <c r="AM6" t="n">
-        <v>8088888.888888889</v>
+        <v>6322222.222222222</v>
       </c>
       <c r="AN6" t="n">
-        <v>77</v>
+        <v>76.66666666666667</v>
       </c>
       <c r="AO6" t="n">
-        <v>25.14285714285714</v>
+        <v>23.76923076923077</v>
       </c>
       <c r="AP6" t="n">
-        <v>181</v>
+        <v>185.6923076923077</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1.538461538461539</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>73.92307692307692</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>9307692.307692308</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>78.46153846153847</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>72.05</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>3926250</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>187</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>351</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>27625000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>392</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>190</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>1</v>
       </c>
-      <c r="AR6" t="n">
-        <v>66.28571428571429</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1228571.428571429</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>69.57142857142857</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>23.1875</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>181.3125</v>
-      </c>
-      <c r="AW6" t="n">
+      <c r="BK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>75</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42100</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="M7" t="n">
+        <v>48</v>
+      </c>
+      <c r="N7" t="n">
+        <v>52</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>11</v>
+      </c>
+      <c r="T7" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>59</v>
+      </c>
+      <c r="X7" t="n">
+        <v>591</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="AC7" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5600000</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>186.6</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>31650000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>187</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2940000</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>78</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>26015000</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>83.34999999999999</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>26.66666666666667</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>184</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>223</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>227</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>143</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>jLJDHgod</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.64583333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fritz walter stadion
+  kaiserslautern </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>49500</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2y0u8Wrq</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M8" t="n">
+        <v>39</v>
+      </c>
+      <c r="N8" t="n">
+        <v>61</v>
+      </c>
+      <c r="O8" t="n">
+        <v>24</v>
+      </c>
+      <c r="P8" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8</v>
+      </c>
+      <c r="S8" t="n">
+        <v>6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>10</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>4bJLk19p</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>YmfcAeCo</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>59</v>
+      </c>
+      <c r="X8" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>185.2727272727273</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>68.45454545454545</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1620454.545454545</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>71.18181818181819</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>2620000</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>25.57142857142857</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>68.04761904761905</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1578571.428571429</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>70.47619047619048</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>24.36842105263158</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>184.7894736842105</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>1.157894736842105</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>68.52631578947368</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>1851315.789473684</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>74.84210526315789</v>
+      </c>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>A33XyOWA</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.33333333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">benen l 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">waldstadion kaiserlinde
+  spiesen elversberg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>9970</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9443</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6in2Eknb</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M9" t="n">
+        <v>50</v>
+      </c>
+      <c r="N9" t="n">
+        <v>50</v>
+      </c>
+      <c r="O9" t="n">
+        <v>17</v>
+      </c>
+      <c r="P9" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
+        <v>17</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>MDhPV0RQ</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>59</v>
+      </c>
+      <c r="X9" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="AC9" t="n">
+        <v>23.81818181818182</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>182.5454545454545</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>66.09090909090909</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1179545.454545455</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>71.81818181818181</v>
+      </c>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="n">
+        <v>25.64705882352941</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>185.0588235294118</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>67.05882352941177</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1364705.882352941</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>70.35294117647059</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>23.83333333333333</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1918750</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>74.16666666666667</v>
+      </c>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0Ug8yfLU</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.33333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volksparkstadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>57274</v>
+      </c>
+      <c r="F10" t="n">
+        <v>57000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M10" t="n">
+        <v>63</v>
+      </c>
+      <c r="N10" t="n">
+        <v>37</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" t="n">
+        <v>13</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>59</v>
+      </c>
+      <c r="X10" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="n">
+        <v>25.625</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>185.625</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2725000</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>185.7333333333333</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>70.66666666666667</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2838666.666666667</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>66</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1269444.444444444</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fgQ4JFGq</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.33333333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych d  f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">max morlock stadion
+  nuremberg </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31581</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M11" t="n">
+        <v>42</v>
+      </c>
+      <c r="N11" t="n">
+        <v>58</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>12</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>tO31cZrF</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>59</v>
+      </c>
+      <c r="X11" t="n">
+        <v>592</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.125</v>
       </c>
-      <c r="AX6" t="n">
-        <v>72.75</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>7993750</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>79.25</v>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
-      <c r="BI6" t="inlineStr"/>
-      <c r="BJ6" t="inlineStr"/>
-      <c r="BK6" t="inlineStr"/>
-      <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
+      <c r="AF11" t="n">
+        <v>67.75</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>2181250</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>74.125</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>179.75</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>68</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1450000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>71.125</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>177.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2230000</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>25.05882352941176</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>178.8235294117647</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>66.76470588235294</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1272058.823529412</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>69</v>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN12"/>
+  <dimension ref="A1:CN8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,144 +892,144 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45571.60416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29546</v>
+        <v>60449</v>
       </c>
       <c r="F2" t="n">
-        <v>29546</v>
+        <v>58000</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M2" t="n">
+        <v>62</v>
+      </c>
+      <c r="N2" t="n">
+        <v>38</v>
+      </c>
+      <c r="O2" t="n">
+        <v>18</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>11</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>10</v>
+      </c>
+      <c r="W2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X2" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="M2" t="n">
-        <v>56</v>
-      </c>
-      <c r="N2" t="n">
-        <v>44</v>
-      </c>
-      <c r="O2" t="n">
-        <v>17</v>
-      </c>
-      <c r="P2" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q2" t="n">
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC2" t="n">
         <v>4</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AD2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
         <v>4</v>
       </c>
-      <c r="S2" t="n">
-        <v>13</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U2" t="n">
-        <v>20</v>
-      </c>
-      <c r="V2" t="n">
-        <v>15</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>3</v>
-      </c>
       <c r="AI2" t="n">
-        <v>488</v>
+        <v>712</v>
       </c>
       <c r="AJ2" t="n">
-        <v>408</v>
+        <v>319</v>
       </c>
       <c r="AK2" t="n">
-        <v>386</v>
+        <v>655</v>
       </c>
       <c r="AL2" t="n">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="AM2" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="AN2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -1047,279 +1047,279 @@
       <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="n">
-        <v>26.63636363636364</v>
+        <v>24.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>184.5454545454545</v>
+        <v>185.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>71.18181818181819</v>
+        <v>75.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17636.36363636364</v>
+        <v>26400</v>
       </c>
       <c r="BA2" t="n">
-        <v>2509090.909090909</v>
+        <v>13632500</v>
       </c>
       <c r="BB2" t="n">
-        <v>74</v>
+        <v>79.8</v>
       </c>
       <c r="BC2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>26.9</v>
+        <v>26.55555555555556</v>
       </c>
       <c r="BE2" t="n">
-        <v>183</v>
+        <v>186.1111111111111</v>
       </c>
       <c r="BF2" t="n">
-        <v>74.5</v>
+        <v>74.44444444444444</v>
       </c>
       <c r="BG2" t="n">
-        <v>25800</v>
+        <v>28888.88888888889</v>
       </c>
       <c r="BH2" t="n">
-        <v>6410000</v>
+        <v>7488888.888888889</v>
       </c>
       <c r="BI2" t="n">
-        <v>77.3</v>
+        <v>79</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1.4</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="BK2" t="n">
-        <v>25.89473684210526</v>
+        <v>24.52631578947368</v>
       </c>
       <c r="BL2" t="n">
-        <v>185.0526315789474</v>
+        <v>187.2105263157895</v>
       </c>
       <c r="BM2" t="n">
-        <v>67.36842105263158</v>
+        <v>74.73684210526316</v>
       </c>
       <c r="BN2" t="n">
-        <v>15421.05263157895</v>
+        <v>24578.94736842105</v>
       </c>
       <c r="BO2" t="n">
-        <v>1536842.105263158</v>
+        <v>10726315.78947368</v>
       </c>
       <c r="BP2" t="n">
-        <v>71.31578947368421</v>
+        <v>78.21052631578948</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1</v>
+        <v>1.473684210526316</v>
       </c>
       <c r="BR2" t="n">
-        <v>23.86666666666667</v>
+        <v>23.71428571428572</v>
       </c>
       <c r="BS2" t="n">
-        <v>182.5333333333333</v>
+        <v>184.952380952381</v>
       </c>
       <c r="BT2" t="n">
-        <v>70.59999999999999</v>
+        <v>70.28571428571429</v>
       </c>
       <c r="BU2" t="n">
-        <v>20266.66666666667</v>
+        <v>20571.42857142857</v>
       </c>
       <c r="BV2" t="n">
-        <v>4328333.333333333</v>
+        <v>4213095.238095238</v>
       </c>
       <c r="BW2" t="n">
-        <v>78.86666666666666</v>
+        <v>78.19047619047619</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.133333333333333</v>
+        <v>1.095238095238095</v>
       </c>
       <c r="BY2" t="n">
-        <v>29.6</v>
+        <v>22.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>187</v>
+        <v>183.75</v>
       </c>
       <c r="CA2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CB2" t="n">
-        <v>326</v>
+        <v>281</v>
       </c>
       <c r="CC2" t="n">
         <v>71000</v>
       </c>
       <c r="CD2" t="n">
-        <v>3310000</v>
+        <v>19600000</v>
       </c>
       <c r="CE2" t="n">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="CF2" t="n">
         <v>5</v>
       </c>
       <c r="CG2" t="n">
-        <v>27</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="CH2" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="CI2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CJ2" t="n">
-        <v>76</v>
+        <v>447</v>
       </c>
       <c r="CK2" t="n">
-        <v>26000</v>
+        <v>174000</v>
       </c>
       <c r="CL2" t="n">
-        <v>8000000</v>
+        <v>35200000</v>
       </c>
       <c r="CM2" t="n">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="CN2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30210</v>
+        <v>58000</v>
       </c>
       <c r="F3" t="n">
-        <v>30210</v>
+        <v>58000</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2.13</v>
+        <v>0.89</v>
       </c>
       <c r="L3" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="M3" t="n">
+        <v>33</v>
+      </c>
+      <c r="N3" t="n">
         <v>67</v>
       </c>
-      <c r="N3" t="n">
-        <v>33</v>
-      </c>
       <c r="O3" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="S3" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U3" t="n">
         <v>11</v>
       </c>
       <c r="V3" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="W3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="Y3" t="n">
         <v>3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AA3" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="AB3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC3" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" t="n">
-        <v>2</v>
-      </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>814</v>
+        <v>305</v>
       </c>
       <c r="AJ3" t="n">
-        <v>277</v>
+        <v>863</v>
       </c>
       <c r="AK3" t="n">
-        <v>749</v>
+        <v>238</v>
       </c>
       <c r="AL3" t="n">
-        <v>208</v>
+        <v>768</v>
       </c>
       <c r="AM3" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AN3" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -1337,263 +1337,277 @@
       <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="n">
-        <v>26.7</v>
+        <v>23.44444444444444</v>
       </c>
       <c r="AX3" t="n">
-        <v>183.9</v>
+        <v>186.6666666666667</v>
       </c>
       <c r="AY3" t="n">
-        <v>84.59999999999999</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="AZ3" t="n">
-        <v>105600</v>
+        <v>31444.44444444445</v>
       </c>
       <c r="BA3" t="n">
-        <v>55100000</v>
+        <v>14466666.66666667</v>
       </c>
       <c r="BB3" t="n">
-        <v>86.40000000000001</v>
+        <v>81.55555555555556</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.3</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="BD3" t="n">
-        <v>26.66666666666667</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="BE3" t="n">
-        <v>184.7777777777778</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="BF3" t="n">
-        <v>70.11111111111111</v>
+        <v>82.88888888888889</v>
       </c>
       <c r="BG3" t="n">
-        <v>16888.88888888889</v>
+        <v>78444.44444444444</v>
       </c>
       <c r="BH3" t="n">
-        <v>2011111.111111111</v>
+        <v>40444444.44444445</v>
       </c>
       <c r="BI3" t="n">
-        <v>73</v>
+        <v>85.22222222222223</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>3.222222222222222</v>
       </c>
       <c r="BK3" t="n">
-        <v>24.8</v>
+        <v>24</v>
       </c>
       <c r="BL3" t="n">
-        <v>182.2</v>
+        <v>182.9047619047619</v>
       </c>
       <c r="BM3" t="n">
-        <v>80.73333333333333</v>
+        <v>73.42857142857143</v>
       </c>
       <c r="BN3" t="n">
-        <v>80733.33333333333</v>
+        <v>27857.14285714286</v>
       </c>
       <c r="BO3" t="n">
-        <v>33733333.33333334</v>
+        <v>8866190.476190476</v>
       </c>
       <c r="BP3" t="n">
-        <v>84.2</v>
+        <v>80.42857142857143</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.2</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="BR3" t="n">
-        <v>26.39130434782609</v>
+        <v>25.6</v>
       </c>
       <c r="BS3" t="n">
-        <v>184.7826086956522</v>
+        <v>184</v>
       </c>
       <c r="BT3" t="n">
-        <v>68.78260869565217</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>16391.30434782609</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="n">
-        <v>1804347.826086957</v>
+        <v>32325000</v>
       </c>
       <c r="BW3" t="n">
-        <v>71.91304347826087</v>
+        <v>84.05</v>
       </c>
       <c r="BX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY3" t="inlineStr"/>
-      <c r="BZ3" t="inlineStr"/>
-      <c r="CA3" t="inlineStr"/>
-      <c r="CB3" t="inlineStr"/>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="inlineStr"/>
-      <c r="CF3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>19</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>172</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>59</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>575000</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>76</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>1</v>
+      </c>
       <c r="CG3" t="n">
-        <v>25.5</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="CH3" t="n">
-        <v>190</v>
+        <v>183.5</v>
       </c>
       <c r="CI3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CJ3" t="n">
-        <v>136</v>
+        <v>444</v>
       </c>
       <c r="CK3" t="n">
-        <v>27000</v>
+        <v>276000</v>
       </c>
       <c r="CL3" t="n">
-        <v>3500000</v>
+        <v>189150000</v>
       </c>
       <c r="CM3" t="n">
-        <v>145</v>
+        <v>498</v>
       </c>
       <c r="CN3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>15000</v>
       </c>
       <c r="F4" t="n">
-        <v>24630</v>
+        <v>15000</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2.01</v>
+        <v>1.46</v>
       </c>
       <c r="L4" t="n">
-        <v>3.41</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="N4" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="O4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T4" t="n">
         <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="V4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="X4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA4" t="n">
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>4</v>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>391</v>
+        <v>408</v>
       </c>
       <c r="AJ4" t="n">
-        <v>286</v>
+        <v>491</v>
       </c>
       <c r="AK4" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="AL4" t="n">
-        <v>206</v>
+        <v>393</v>
       </c>
       <c r="AM4" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="AN4" t="n">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -1611,272 +1625,286 @@
       <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="n">
-        <v>29.75</v>
+        <v>26.8</v>
       </c>
       <c r="AX4" t="n">
+        <v>188.1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>22300</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3280000</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>183.7777777777778</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>81.22222222222223</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>59777.77777777778</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>33944444.44444445</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>84.55555555555556</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>26.47826086956522</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>184.5217391304348</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>69.04347826086956</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>19826.08695652174</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1771739.130434783</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>71.04347826086956</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>25.10526315789474</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>184</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>78.68421052631579</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>52052.63157894737</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>24642105.26315789</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>82.68421052631579</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1.842105263157895</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>25</v>
+      </c>
+      <c r="BZ4" t="n">
         <v>186</v>
       </c>
-      <c r="AY4" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>17500</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>2090625</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>73.125</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
-      <c r="BI4" t="inlineStr"/>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="n">
-        <v>26.38461538461538</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>186.1538461538462</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>69.61538461538461</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>16230.76923076923</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>2009615.384615385</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>74.30769230769231</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>24.95454545454545</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>183.7727272727273</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>74.09090909090909</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>33454.54545454546</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>8279545.454545454</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>78.22727272727273</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>1.545454545454545</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>185.5</v>
-      </c>
       <c r="CA4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CB4" t="n">
-        <v>136</v>
+        <v>279</v>
       </c>
       <c r="CC4" t="n">
-        <v>32000</v>
+        <v>80000</v>
       </c>
       <c r="CD4" t="n">
-        <v>5575000</v>
+        <v>12100000</v>
       </c>
       <c r="CE4" t="n">
-        <v>147</v>
+        <v>294</v>
       </c>
       <c r="CF4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CG4" t="n">
-        <v>23.5</v>
+        <v>25.66666666666667</v>
       </c>
       <c r="CH4" t="n">
-        <v>182.25</v>
+        <v>181</v>
       </c>
       <c r="CI4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="CJ4" t="n">
-        <v>294</v>
+        <v>228</v>
       </c>
       <c r="CK4" t="n">
-        <v>140000</v>
+        <v>132000</v>
       </c>
       <c r="CL4" t="n">
-        <v>42300000</v>
+        <v>40500000</v>
       </c>
       <c r="CM4" t="n">
-        <v>318</v>
+        <v>248</v>
       </c>
       <c r="CN4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>2g2Log1S</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.35416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22012</v>
+        <v>23325</v>
       </c>
       <c r="F5" t="n">
-        <v>22012</v>
+        <v>19919</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>1.57</v>
+        <v>4.24</v>
       </c>
       <c r="L5" t="n">
-        <v>0.95</v>
+        <v>1.59</v>
       </c>
       <c r="M5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O5" t="n">
+        <v>22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>12</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="n">
+        <v>16</v>
+      </c>
+      <c r="U5" t="n">
+        <v>18</v>
+      </c>
+      <c r="V5" t="n">
+        <v>18</v>
+      </c>
+      <c r="W5" t="n">
+        <v>6</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF5" t="n">
         <v>13</v>
       </c>
-      <c r="P5" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4</v>
-      </c>
-      <c r="U5" t="n">
-        <v>16</v>
-      </c>
-      <c r="V5" t="n">
-        <v>19</v>
-      </c>
-      <c r="W5" t="n">
-        <v>3</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>17</v>
-      </c>
       <c r="AG5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
         <v>4</v>
       </c>
       <c r="AI5" t="n">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="AJ5" t="n">
-        <v>602</v>
+        <v>486</v>
       </c>
       <c r="AK5" t="n">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="AL5" t="n">
-        <v>512</v>
+        <v>379</v>
       </c>
       <c r="AM5" t="n">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="AN5" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>t0ZPdkUl</t>
         </is>
       </c>
       <c r="AQ5" t="n">
         <v>59</v>
       </c>
       <c r="AR5" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -1887,286 +1915,270 @@
       <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>26.27272727272727</v>
+        <v>26.3</v>
       </c>
       <c r="AX5" t="n">
-        <v>186.4545454545455</v>
+        <v>183.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>74.09090909090909</v>
+        <v>68.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>25090.90909090909</v>
+        <v>11400</v>
       </c>
       <c r="BA5" t="n">
-        <v>5718181.818181818</v>
+        <v>1525000</v>
       </c>
       <c r="BB5" t="n">
-        <v>77.90909090909091</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.363636363636364</v>
+        <v>1</v>
       </c>
       <c r="BD5" t="n">
-        <v>26.2</v>
+        <v>27.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>186.1</v>
+        <v>184.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>81.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="BG5" t="n">
-        <v>56900</v>
+        <v>19600</v>
       </c>
       <c r="BH5" t="n">
-        <v>37400000</v>
+        <v>2175000</v>
       </c>
       <c r="BI5" t="n">
-        <v>84.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="BJ5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="BK5" t="n">
-        <v>26.88888888888889</v>
+        <v>26.94736842105263</v>
       </c>
       <c r="BL5" t="n">
-        <v>182.2777777777778</v>
+        <v>187.2631578947368</v>
       </c>
       <c r="BM5" t="n">
-        <v>73.22222222222223</v>
+        <v>67</v>
       </c>
       <c r="BN5" t="n">
-        <v>26444.44444444445</v>
+        <v>8842.105263157895</v>
       </c>
       <c r="BO5" t="n">
-        <v>4133333.333333333</v>
+        <v>1151315.789473684</v>
       </c>
       <c r="BP5" t="n">
-        <v>75.11111111111111</v>
+        <v>69.84210526315789</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.055555555555556</v>
+        <v>1</v>
       </c>
       <c r="BR5" t="n">
-        <v>26.73684210526316</v>
+        <v>24.65217391304348</v>
       </c>
       <c r="BS5" t="n">
-        <v>184.6315789473684</v>
+        <v>181.5217391304348</v>
       </c>
       <c r="BT5" t="n">
-        <v>79.21052631578948</v>
+        <v>68.8695652173913</v>
       </c>
       <c r="BU5" t="n">
-        <v>49578.94736842105</v>
+        <v>18782.60869565217</v>
       </c>
       <c r="BV5" t="n">
-        <v>23531578.94736842</v>
+        <v>2058695.652173913</v>
       </c>
       <c r="BW5" t="n">
-        <v>82.10526315789474</v>
+        <v>73.82608695652173</v>
       </c>
       <c r="BX5" t="n">
-        <v>2.157894736842105</v>
+        <v>1</v>
       </c>
       <c r="BY5" t="n">
-        <v>29</v>
+        <v>23.75</v>
       </c>
       <c r="BZ5" t="n">
-        <v>180.3333333333333</v>
+        <v>186.5</v>
       </c>
       <c r="CA5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CB5" t="n">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="CC5" t="n">
-        <v>94000</v>
+        <v>28000</v>
       </c>
       <c r="CD5" t="n">
-        <v>15100000</v>
+        <v>3900000</v>
       </c>
       <c r="CE5" t="n">
-        <v>222</v>
+        <v>293</v>
       </c>
       <c r="CF5" t="n">
         <v>4</v>
       </c>
-      <c r="CG5" t="n">
-        <v>20.33333333333333</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>178.3333333333333</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>3</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>220</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>86000</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>49700000</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>255</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>5</v>
-      </c>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>dEtNxbIc</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.35416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">merkur spiel arena
+  dusseldorf </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42100</v>
+        <v>54600</v>
       </c>
       <c r="F6" t="n">
-        <v>41200</v>
+        <v>51500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.84</v>
+        <v>2.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.12</v>
+        <v>2.54</v>
       </c>
       <c r="M6" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="N6" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="P6" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="n">
         <v>13</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>3</v>
-      </c>
-      <c r="S6" t="n">
-        <v>8</v>
-      </c>
-      <c r="T6" t="n">
-        <v>10</v>
       </c>
       <c r="U6" t="n">
         <v>11</v>
       </c>
       <c r="V6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AB6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
         <v>2</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>612</v>
+        <v>465</v>
       </c>
       <c r="AJ6" t="n">
-        <v>419</v>
+        <v>511</v>
       </c>
       <c r="AK6" t="n">
-        <v>539</v>
+        <v>414</v>
       </c>
       <c r="AL6" t="n">
-        <v>360</v>
+        <v>460</v>
       </c>
       <c r="AM6" t="n">
+        <v>115</v>
+      </c>
+      <c r="AN6" t="n">
         <v>116</v>
       </c>
-      <c r="AN6" t="n">
-        <v>122</v>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
       <c r="AQ6" t="n">
         <v>59</v>
       </c>
       <c r="AR6" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -2174,289 +2186,293 @@
       <c r="AT6" t="n">
         <v>20242025</v>
       </c>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
       <c r="AW6" t="n">
-        <v>26.45454545454545</v>
+        <v>27.22222222222222</v>
       </c>
       <c r="AX6" t="n">
-        <v>184.5454545454545</v>
+        <v>183.2222222222222</v>
       </c>
       <c r="AY6" t="n">
-        <v>73.81818181818181</v>
+        <v>69.88888888888889</v>
       </c>
       <c r="AZ6" t="n">
-        <v>23545.45454545454</v>
+        <v>18111.11111111111</v>
       </c>
       <c r="BA6" t="n">
-        <v>5818181.818181818</v>
+        <v>1833333.333333333</v>
       </c>
       <c r="BB6" t="n">
-        <v>76.90909090909091</v>
+        <v>73</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="BD6" t="n">
-        <v>27.1</v>
+        <v>26.90909090909091</v>
       </c>
       <c r="BE6" t="n">
-        <v>184.1</v>
+        <v>183.5454545454545</v>
       </c>
       <c r="BF6" t="n">
-        <v>76.90000000000001</v>
+        <v>71.72727272727273</v>
       </c>
       <c r="BG6" t="n">
-        <v>27400</v>
+        <v>21818.18181818182</v>
       </c>
       <c r="BH6" t="n">
-        <v>11860000</v>
+        <v>2809090.909090909</v>
       </c>
       <c r="BI6" t="n">
-        <v>79</v>
+        <v>73.90909090909091</v>
       </c>
       <c r="BJ6" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="BK6" t="n">
-        <v>25.55</v>
+        <v>25</v>
       </c>
       <c r="BL6" t="n">
-        <v>184</v>
+        <v>186.421052631579</v>
       </c>
       <c r="BM6" t="n">
-        <v>70.40000000000001</v>
+        <v>68.63157894736842</v>
       </c>
       <c r="BN6" t="n">
-        <v>19300</v>
+        <v>18000</v>
       </c>
       <c r="BO6" t="n">
-        <v>2860000</v>
+        <v>2156578.947368421</v>
       </c>
       <c r="BP6" t="n">
-        <v>74.95</v>
+        <v>73.84210526315789</v>
       </c>
       <c r="BQ6" t="n">
         <v>1</v>
       </c>
       <c r="BR6" t="n">
-        <v>26.34782608695652</v>
+        <v>24.7</v>
       </c>
       <c r="BS6" t="n">
-        <v>183.4347826086957</v>
+        <v>181.6</v>
       </c>
       <c r="BT6" t="n">
-        <v>73.1304347826087</v>
+        <v>69</v>
       </c>
       <c r="BU6" t="n">
-        <v>22130.4347826087</v>
+        <v>18850</v>
       </c>
       <c r="BV6" t="n">
-        <v>5030434.782608695</v>
+        <v>2117500</v>
       </c>
       <c r="BW6" t="n">
-        <v>76.8695652173913</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="BX6" t="n">
-        <v>1.260869565217391</v>
+        <v>1</v>
       </c>
       <c r="BY6" t="n">
-        <v>24.6</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="BZ6" t="n">
-        <v>187</v>
+        <v>188.6666666666667</v>
       </c>
       <c r="CA6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CB6" t="n">
-        <v>350</v>
+        <v>202</v>
       </c>
       <c r="CC6" t="n">
-        <v>87000</v>
+        <v>54000</v>
       </c>
       <c r="CD6" t="n">
-        <v>15700000</v>
+        <v>5750000</v>
       </c>
       <c r="CE6" t="n">
-        <v>380</v>
+        <v>231</v>
       </c>
       <c r="CF6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="CG6" t="n">
-        <v>26.8</v>
+        <v>21</v>
       </c>
       <c r="CH6" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="CI6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CJ6" t="n">
-        <v>354</v>
+        <v>60</v>
       </c>
       <c r="CK6" t="n">
-        <v>91000</v>
+        <v>12000</v>
       </c>
       <c r="CL6" t="n">
-        <v>19700000</v>
+        <v>525000</v>
       </c>
       <c r="CM6" t="n">
-        <v>369</v>
+        <v>69</v>
       </c>
       <c r="CN6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>6R8CmFWF</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45569.64583333334</v>
+        <v>45571.35416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">avnet arena
+  magdeburg </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30660</v>
+        <v>25910</v>
       </c>
       <c r="F7" t="n">
-        <v>30660</v>
+        <v>22615</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1.3</v>
+        <v>3.64</v>
       </c>
       <c r="L7" t="n">
-        <v>0.65</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="N7" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
       </c>
       <c r="T7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="U7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V7" t="n">
         <v>18</v>
       </c>
       <c r="W7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG7" t="n">
         <v>3</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2</v>
-      </c>
       <c r="AH7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>398</v>
+        <v>534</v>
       </c>
       <c r="AJ7" t="n">
-        <v>735</v>
+        <v>331</v>
       </c>
       <c r="AK7" t="n">
-        <v>291</v>
+        <v>481</v>
       </c>
       <c r="AL7" t="n">
-        <v>610</v>
+        <v>275</v>
       </c>
       <c r="AM7" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AN7" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>IgZoGKFn</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
       <c r="AQ7" t="n">
         <v>59</v>
       </c>
       <c r="AR7" t="n">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -2466,266 +2482,280 @@
       </c>
       <c r="AU7" t="inlineStr"/>
       <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
+      <c r="AW7" t="n">
+        <v>25.77777777777778</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>181.3333333333333</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>67.55555555555556</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>10555.55555555555</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1336111.111111111</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>70.55555555555556</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1</v>
+      </c>
       <c r="BD7" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>186.3</v>
+        <v>184.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>75.09999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="BG7" t="n">
-        <v>23800</v>
+        <v>8100</v>
       </c>
       <c r="BH7" t="n">
-        <v>7220000</v>
+        <v>1472500</v>
       </c>
       <c r="BI7" t="n">
-        <v>77.5</v>
+        <v>71.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="BK7" t="n">
-        <v>25.45454545454545</v>
+        <v>24</v>
       </c>
       <c r="BL7" t="n">
-        <v>184.4545454545455</v>
+        <v>178.3529411764706</v>
       </c>
       <c r="BM7" t="n">
-        <v>73.18181818181819</v>
+        <v>66.05882352941177</v>
       </c>
       <c r="BN7" t="n">
-        <v>21363.63636363636</v>
+        <v>10117.64705882353</v>
       </c>
       <c r="BO7" t="n">
-        <v>4981818.181818182</v>
+        <v>1270588.235294118</v>
       </c>
       <c r="BP7" t="n">
-        <v>76.45454545454545</v>
+        <v>70.23529411764706</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.090909090909091</v>
+        <v>1</v>
       </c>
       <c r="BR7" t="n">
-        <v>26.09523809523809</v>
+        <v>24.36363636363636</v>
       </c>
       <c r="BS7" t="n">
-        <v>182.3333333333333</v>
+        <v>181.4545454545455</v>
       </c>
       <c r="BT7" t="n">
-        <v>72.95238095238095</v>
+        <v>66.59090909090909</v>
       </c>
       <c r="BU7" t="n">
-        <v>21380.95238095238</v>
+        <v>7363.636363636364</v>
       </c>
       <c r="BV7" t="n">
-        <v>5110952.380952381</v>
+        <v>1498863.636363636</v>
       </c>
       <c r="BW7" t="n">
-        <v>76.61904761904762</v>
+        <v>73</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.142857142857143</v>
+        <v>1</v>
       </c>
       <c r="BY7" t="n">
-        <v>25.66666666666667</v>
+        <v>28.5</v>
       </c>
       <c r="BZ7" t="n">
-        <v>183.1666666666667</v>
+        <v>181</v>
       </c>
       <c r="CA7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CB7" t="n">
-        <v>419</v>
+        <v>139</v>
       </c>
       <c r="CC7" t="n">
-        <v>104000</v>
+        <v>23000</v>
       </c>
       <c r="CD7" t="n">
-        <v>15925000</v>
+        <v>2800000</v>
       </c>
       <c r="CE7" t="n">
-        <v>435</v>
+        <v>141</v>
       </c>
       <c r="CF7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CG7" t="n">
-        <v>23.5</v>
+        <v>21</v>
       </c>
       <c r="CH7" t="n">
-        <v>182.8333333333333</v>
+        <v>180</v>
       </c>
       <c r="CI7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CJ7" t="n">
-        <v>424</v>
+        <v>66</v>
       </c>
       <c r="CK7" t="n">
-        <v>96000</v>
+        <v>6000</v>
       </c>
       <c r="CL7" t="n">
-        <v>39725000</v>
+        <v>1600000</v>
       </c>
       <c r="CM7" t="n">
-        <v>466</v>
+        <v>73</v>
       </c>
       <c r="CN7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>I5SHRX9d</t>
+          <t>pvFATgup</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45570.33333333334</v>
+        <v>45570.64583333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">erbst l 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">waldstadion kaiserlinde
-  spiesen elversberg </t>
+          <t xml:space="preserve">veltins arena
+  gelsenkirchen </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9970</v>
+        <v>62271</v>
       </c>
       <c r="F8" t="n">
-        <v>9502</v>
+        <v>61939</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="L8" t="n">
-        <v>1.4</v>
+        <v>2.23</v>
       </c>
       <c r="M8" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="N8" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q8" t="n">
         <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V8" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
         <v>6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>5</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AA8" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AB8" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AC8" t="n">
         <v>3</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>328</v>
+        <v>455</v>
       </c>
       <c r="AJ8" t="n">
-        <v>394</v>
+        <v>354</v>
       </c>
       <c r="AK8" t="n">
-        <v>249</v>
+        <v>373</v>
       </c>
       <c r="AL8" t="n">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="AM8" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AN8" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>rPmNFwq1</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>YmfcAeCo</t>
         </is>
       </c>
       <c r="AQ8" t="n">
@@ -2743,1282 +2773,136 @@
       <c r="AU8" t="inlineStr"/>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="n">
-        <v>24.27272727272727</v>
+        <v>27.625</v>
       </c>
       <c r="AX8" t="n">
-        <v>183.4545454545455</v>
+        <v>182.875</v>
       </c>
       <c r="AY8" t="n">
-        <v>66.90909090909091</v>
+        <v>69.75</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9727.272727272728</v>
+        <v>9500</v>
       </c>
       <c r="BA8" t="n">
-        <v>1472727.272727273</v>
+        <v>1775000</v>
       </c>
       <c r="BB8" t="n">
-        <v>72.90909090909091</v>
+        <v>71.75</v>
       </c>
       <c r="BC8" t="n">
         <v>1</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>23.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>186.5</v>
+        <v>183.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>69</v>
+        <v>69.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>9900</v>
+        <v>7900</v>
       </c>
       <c r="BH8" t="n">
-        <v>1860000</v>
+        <v>2230000</v>
       </c>
       <c r="BI8" t="n">
-        <v>71.8</v>
+        <v>75.8</v>
       </c>
       <c r="BJ8" t="n">
         <v>1</v>
       </c>
       <c r="BK8" t="n">
-        <v>26</v>
+        <v>26.21428571428572</v>
       </c>
       <c r="BL8" t="n">
-        <v>183.2142857142857</v>
+        <v>183.7142857142857</v>
       </c>
       <c r="BM8" t="n">
-        <v>66.71428571428571</v>
+        <v>68.85714285714286</v>
       </c>
       <c r="BN8" t="n">
-        <v>9142.857142857143</v>
+        <v>9285.714285714286</v>
       </c>
       <c r="BO8" t="n">
-        <v>1296428.571428571</v>
+        <v>1685714.285714286</v>
       </c>
       <c r="BP8" t="n">
-        <v>70</v>
+        <v>72.07142857142857</v>
       </c>
       <c r="BQ8" t="n">
         <v>1</v>
       </c>
       <c r="BR8" t="n">
-        <v>25.42105263157895</v>
+        <v>26.64285714285714</v>
       </c>
       <c r="BS8" t="n">
-        <v>180.6842105263158</v>
+        <v>184.2142857142857</v>
       </c>
       <c r="BT8" t="n">
-        <v>65.84210526315789</v>
+        <v>68.21428571428571</v>
       </c>
       <c r="BU8" t="n">
-        <v>9263.157894736842</v>
+        <v>9285.714285714286</v>
       </c>
       <c r="BV8" t="n">
-        <v>1192105.263157895</v>
+        <v>1487500</v>
       </c>
       <c r="BW8" t="n">
-        <v>69.42105263157895</v>
+        <v>72.21428571428571</v>
       </c>
       <c r="BX8" t="n">
         <v>1</v>
       </c>
       <c r="BY8" t="n">
-        <v>26.66666666666667</v>
+        <v>28.5</v>
       </c>
       <c r="BZ8" t="n">
-        <v>191.3333333333333</v>
+        <v>191</v>
       </c>
       <c r="CA8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CB8" t="n">
-        <v>196</v>
+        <v>137</v>
       </c>
       <c r="CC8" t="n">
-        <v>42000</v>
+        <v>19000</v>
       </c>
       <c r="CD8" t="n">
-        <v>3200000</v>
+        <v>2575000</v>
       </c>
       <c r="CE8" t="n">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="CF8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="CG8" t="n">
-        <v>29</v>
+        <v>25.71428571428572</v>
       </c>
       <c r="CH8" t="n">
-        <v>179.5</v>
+        <v>184.7142857142857</v>
       </c>
       <c r="CI8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CJ8" t="n">
-        <v>270</v>
+        <v>498</v>
       </c>
       <c r="CK8" t="n">
-        <v>41000</v>
+        <v>69000</v>
       </c>
       <c r="CL8" t="n">
-        <v>4150000</v>
+        <v>20500000</v>
       </c>
       <c r="CM8" t="n">
-        <v>273</v>
+        <v>525</v>
       </c>
       <c r="CN8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>4KgyFfQj</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45570.33333333334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">alt p 
-  ger </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rheinenergiestadion
-  cologne </t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F9" t="n">
-        <v>49900</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>tbC3EcQn</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="M9" t="n">
-        <v>55</v>
-      </c>
-      <c r="N9" t="n">
-        <v>45</v>
-      </c>
-      <c r="O9" t="n">
-        <v>21</v>
-      </c>
-      <c r="P9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" t="n">
-        <v>23</v>
-      </c>
-      <c r="W9" t="n">
-        <v>7</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>15</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>545</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>379</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>480</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>303</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>113</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>109</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>4fX0k7gg</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
-        <v>59</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>592</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>185.1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>9500</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4250000</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>77.8</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>186</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>7800</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>880000</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>26.26086956521739</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>185</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>69.30434782608695</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>10217.39130434783</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>2733695.652173913</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>73.30434782608695</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>1.173913043478261</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>26.52631578947368</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>182.2105263157895</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>64.15789473684211</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>7210.526315789473</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>796842.1052631579</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>69.15789473684211</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>185</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>215</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>8700000</v>
-      </c>
-      <c r="CE9" t="n">
-        <v>228</v>
-      </c>
-      <c r="CF9" t="n">
-        <v>3</v>
-      </c>
-      <c r="CG9" t="n">
-        <v>26</v>
-      </c>
-      <c r="CH9" t="n">
-        <v>195</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>2</v>
-      </c>
-      <c r="CJ9" t="n">
-        <v>135</v>
-      </c>
-      <c r="CK9" t="n">
-        <v>9000</v>
-      </c>
-      <c r="CL9" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="CM9" t="n">
-        <v>141</v>
-      </c>
-      <c r="CN9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>YDA4ky23</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45570.33333333334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kampka r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">max morlock stadion
-  nuremberg </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F10" t="n">
-        <v>27312</v>
-      </c>
-      <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M10" t="n">
-        <v>61</v>
-      </c>
-      <c r="N10" t="n">
-        <v>39</v>
-      </c>
-      <c r="O10" t="n">
-        <v>17</v>
-      </c>
-      <c r="P10" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="n">
-        <v>11</v>
-      </c>
-      <c r="U10" t="n">
-        <v>22</v>
-      </c>
-      <c r="V10" t="n">
-        <v>15</v>
-      </c>
-      <c r="W10" t="n">
-        <v>7</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>415</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>243</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>344</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>182</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>111</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>pdPRS0me</t>
-        </is>
-      </c>
-      <c r="AQ10" t="n">
-        <v>59</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>592</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>183.1</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>66</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>8800</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>1130000</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>27</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>180</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>68.25</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>9125</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1401250</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>70.125</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>28.06666666666667</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>183.1333333333333</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>65.13333333333334</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>8066.666666666667</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>781666.6666666666</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>67.53333333333333</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>21</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>181.6666666666667</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>203</v>
-      </c>
-      <c r="CC10" t="n">
-        <v>21000</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>234</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>3</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>25.75</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>181.25</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>4</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>265</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>32000</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>279</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>htzWzxmA</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.5625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lechner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bbbank wildpark
-  karlsruhe </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>34302</v>
-      </c>
-      <c r="F11" t="n">
-        <v>31034</v>
-      </c>
-      <c r="G11" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="L11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="M11" t="n">
-        <v>47</v>
-      </c>
-      <c r="N11" t="n">
-        <v>53</v>
-      </c>
-      <c r="O11" t="n">
-        <v>13</v>
-      </c>
-      <c r="P11" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>9</v>
-      </c>
-      <c r="S11" t="n">
         <v>8</v>
-      </c>
-      <c r="T11" t="n">
-        <v>9</v>
-      </c>
-      <c r="U11" t="n">
-        <v>8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>10</v>
-      </c>
-      <c r="W11" t="n">
-        <v>3</v>
-      </c>
-      <c r="X11" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>468</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>585</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>389</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>515</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>113</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>115</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>OzPMRhK3</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>4dKVOnA1</t>
-        </is>
-      </c>
-      <c r="AQ11" t="n">
-        <v>59</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>592</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="n">
-        <v>27.27272727272727</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>184.1818181818182</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>68.36363636363636</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>10636.36363636364</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>1470454.545454545</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>72.36363636363636</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>24.875</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>187.125</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>69.375</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>11875</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>1937500</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>73.875</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>25.05263157894737</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>182.6315789473684</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>66.47368421052632</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>10894.73684210526</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1279473.684210526</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>71.84210526315789</v>
-      </c>
-      <c r="BQ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR11" t="n">
-        <v>27.36363636363636</v>
-      </c>
-      <c r="BS11" t="n">
-        <v>182.9545454545455</v>
-      </c>
-      <c r="BT11" t="n">
-        <v>68.09090909090909</v>
-      </c>
-      <c r="BU11" t="n">
-        <v>12000</v>
-      </c>
-      <c r="BV11" t="n">
-        <v>1331818.181818182</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>70.59090909090909</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>22.33333333333333</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>183.3333333333333</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>194</v>
-      </c>
-      <c r="CC11" t="n">
-        <v>26000</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>4125000</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>219</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>3</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>183</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>5</v>
-      </c>
-      <c r="CJ11" t="n">
-        <v>352</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>75000</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>369</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>06wvZFHM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45569.5625</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prigan f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">home deluxe arena
-  paderborn </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F12" t="n">
-        <v>12615</v>
-      </c>
-      <c r="G12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="M12" t="n">
-        <v>68</v>
-      </c>
-      <c r="N12" t="n">
-        <v>32</v>
-      </c>
-      <c r="O12" t="n">
-        <v>22</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>9</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>13</v>
-      </c>
-      <c r="T12" t="n">
-        <v>9</v>
-      </c>
-      <c r="U12" t="n">
-        <v>9</v>
-      </c>
-      <c r="V12" t="n">
-        <v>12</v>
-      </c>
-      <c r="W12" t="n">
-        <v>9</v>
-      </c>
-      <c r="X12" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="n">
-        <v>724</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>306</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>652</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>230</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>118</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>116</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>0AI1QUJH</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>zyLSrbZQ</t>
-        </is>
-      </c>
-      <c r="AQ12" t="n">
-        <v>59</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>592</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>185</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>67.8</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13000</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>1580000</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>7300</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>1165000</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>25.21739130434782</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>183.4347826086957</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>66.69565217391305</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>12782.60869565217</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1260869.565217391</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>71.04347826086956</v>
-      </c>
-      <c r="BQ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR12" t="n">
-        <v>27.35714285714286</v>
-      </c>
-      <c r="BS12" t="n">
-        <v>184.2142857142857</v>
-      </c>
-      <c r="BT12" t="n">
-        <v>65.28571428571429</v>
-      </c>
-      <c r="BU12" t="n">
-        <v>8428.571428571429</v>
-      </c>
-      <c r="BV12" t="n">
-        <v>878571.4285714285</v>
-      </c>
-      <c r="BW12" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="BX12" t="n">
-        <v>1</v>
-      </c>
-      <c r="BY12" t="n">
-        <v>23</v>
-      </c>
-      <c r="BZ12" t="n">
-        <v>187.6666666666667</v>
-      </c>
-      <c r="CA12" t="n">
-        <v>3</v>
-      </c>
-      <c r="CB12" t="n">
-        <v>197</v>
-      </c>
-      <c r="CC12" t="n">
-        <v>31000</v>
-      </c>
-      <c r="CD12" t="n">
-        <v>4225000</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>220</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>3</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>27.75</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>4</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>248</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>29000</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>2420000</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>266</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
+++ b/data/germany/p6_deployment/missing/data_preparation/df_integrated_missing.xlsx
@@ -600,92 +600,92 @@
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>total_passes_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>completed_passes_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>crosses_completed_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>interceptions_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
           <t>red_cards_home</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>red_cards_away</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_home</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_home</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_home</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_away</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_away</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
@@ -922,609 +922,623 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>zyC4c6ee</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45592.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28917</v>
+        <v>15000</v>
       </c>
       <c r="F2" t="n">
-        <v>28917</v>
+        <v>15000</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M2" t="n">
+        <v>47</v>
+      </c>
+      <c r="N2" t="n">
+        <v>53</v>
+      </c>
+      <c r="O2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>4</v>
+      </c>
+      <c r="S2" t="n">
+        <v>12</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>4</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="M2" t="n">
-        <v>43</v>
-      </c>
-      <c r="N2" t="n">
-        <v>57</v>
-      </c>
-      <c r="O2" t="n">
-        <v>14</v>
-      </c>
-      <c r="P2" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="V2" t="n">
+        <v>5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>16</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y2" t="n">
         <v>7</v>
       </c>
-      <c r="S2" t="n">
-        <v>7</v>
-      </c>
-      <c r="T2" t="n">
-        <v>4</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>4</v>
-      </c>
-      <c r="W2" t="n">
-        <v>9</v>
-      </c>
-      <c r="X2" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4</v>
-      </c>
       <c r="Z2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AD2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF2" t="n">
         <v>3</v>
       </c>
-      <c r="AF2" t="n">
-        <v>4</v>
-      </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AI2" t="n">
         <v>1</v>
       </c>
       <c r="AJ2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>379</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>445</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>290</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>355</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW2" t="n">
         <v>0</v>
       </c>
-      <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>390</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>533</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>302</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>436</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="AW2" t="n">
-        <v>59</v>
-      </c>
       <c r="AX2" t="n">
-        <v>591</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
         <v>20242025</v>
       </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
+      <c r="BC2" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>185.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>22700</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3710000</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.1</v>
+      </c>
       <c r="BJ2" t="n">
-        <v>27.2</v>
+        <v>27.22222222222222</v>
       </c>
       <c r="BK2" t="n">
-        <v>181.9</v>
+        <v>185.8888888888889</v>
       </c>
       <c r="BL2" t="n">
-        <v>74.09999999999999</v>
+        <v>75.44444444444444</v>
       </c>
       <c r="BM2" t="n">
-        <v>22600</v>
+        <v>30000</v>
       </c>
       <c r="BN2" t="n">
-        <v>5690000</v>
+        <v>7733333.333333333</v>
       </c>
       <c r="BO2" t="n">
-        <v>76.40000000000001</v>
+        <v>79.22222222222223</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.1</v>
+        <v>1.555555555555556</v>
       </c>
       <c r="BQ2" t="n">
-        <v>25.21052631578947</v>
+        <v>25.64705882352941</v>
       </c>
       <c r="BR2" t="n">
-        <v>185.2631578947368</v>
+        <v>185.1764705882353</v>
       </c>
       <c r="BS2" t="n">
-        <v>73.68421052631579</v>
+        <v>68.70588235294117</v>
       </c>
       <c r="BT2" t="n">
-        <v>34368.42105263158</v>
+        <v>19470.58823529412</v>
       </c>
       <c r="BU2" t="n">
-        <v>9086842.105263159</v>
+        <v>1967647.058823529</v>
       </c>
       <c r="BV2" t="n">
-        <v>78.42105263157895</v>
+        <v>72</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.526315789473684</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="BX2" t="n">
-        <v>24.31818181818182</v>
+        <v>25.75</v>
       </c>
       <c r="BY2" t="n">
-        <v>185.8181818181818</v>
+        <v>182.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>70.22727272727273</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="CA2" t="n">
-        <v>20409.09090909091</v>
+        <v>26150</v>
       </c>
       <c r="CB2" t="n">
-        <v>3536363.636363636</v>
+        <v>5920000</v>
       </c>
       <c r="CC2" t="n">
-        <v>76</v>
+        <v>77.95</v>
       </c>
       <c r="CD2" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="CE2" t="n">
-        <v>23.8</v>
+        <v>22</v>
       </c>
       <c r="CF2" t="n">
-        <v>182.8</v>
+        <v>184.5</v>
       </c>
       <c r="CG2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CH2" t="n">
-        <v>371</v>
+        <v>125</v>
       </c>
       <c r="CI2" t="n">
-        <v>181000</v>
+        <v>28000</v>
       </c>
       <c r="CJ2" t="n">
-        <v>56300000</v>
+        <v>1575000</v>
       </c>
       <c r="CK2" t="n">
-        <v>398</v>
+        <v>140</v>
       </c>
       <c r="CL2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="CM2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="CN2" t="n">
-        <v>187.4</v>
+        <v>183</v>
       </c>
       <c r="CO2" t="n">
         <v>5</v>
       </c>
       <c r="CP2" t="n">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="CQ2" t="n">
-        <v>112000</v>
+        <v>128000</v>
       </c>
       <c r="CR2" t="n">
-        <v>20100000</v>
+        <v>31400000</v>
       </c>
       <c r="CS2" t="n">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="CT2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>ABBmcc1C</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45592.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15034</v>
+        <v>22012</v>
       </c>
       <c r="F3" t="n">
-        <v>15034</v>
+        <v>22012</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="M3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+      <c r="R3" t="n">
         <v>5</v>
       </c>
-      <c r="R3" t="n">
-        <v>4</v>
-      </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
         <v>6</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3" t="n">
+        <v>6</v>
+      </c>
+      <c r="W3" t="n">
+        <v>7</v>
+      </c>
+      <c r="X3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y3" t="n">
         <v>4</v>
       </c>
-      <c r="W3" t="n">
-        <v>11</v>
-      </c>
-      <c r="X3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH3" t="n">
         <v>7</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AI3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>3</v>
       </c>
-      <c r="AA3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AK3" t="n">
+        <v>448</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>492</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>333</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>379</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP3" t="n">
         <v>4</v>
       </c>
-      <c r="AC3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>433</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>480</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>344</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>392</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
+        <v>13</v>
+      </c>
+      <c r="AS3" t="inlineStr">
         <is>
           <t>hpYJ6izc</t>
         </is>
       </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>591</v>
+      </c>
       <c r="AW3" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>591</v>
+        <v>20242025</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20242025</v>
+        <v>1</v>
       </c>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
       <c r="BC3" t="n">
-        <v>25.77777777777778</v>
+        <v>26.27272727272727</v>
       </c>
       <c r="BD3" t="n">
-        <v>187.5555555555555</v>
+        <v>186.4545454545455</v>
       </c>
       <c r="BE3" t="n">
-        <v>69.44444444444444</v>
+        <v>74.09090909090909</v>
       </c>
       <c r="BF3" t="n">
-        <v>16000</v>
+        <v>25090.90909090909</v>
       </c>
       <c r="BG3" t="n">
-        <v>1877777.777777778</v>
+        <v>5718181.818181818</v>
       </c>
       <c r="BH3" t="n">
-        <v>72.11111111111111</v>
+        <v>77.90909090909091</v>
       </c>
       <c r="BI3" t="n">
-        <v>1</v>
+        <v>1.363636363636364</v>
       </c>
       <c r="BJ3" t="n">
-        <v>26.54545454545455</v>
+        <v>25.125</v>
       </c>
       <c r="BK3" t="n">
-        <v>186.6363636363636</v>
+        <v>184.625</v>
       </c>
       <c r="BL3" t="n">
-        <v>74.18181818181819</v>
+        <v>77.625</v>
       </c>
       <c r="BM3" t="n">
-        <v>25909.09090909091</v>
+        <v>37000</v>
       </c>
       <c r="BN3" t="n">
-        <v>5709090.909090909</v>
+        <v>15312500</v>
       </c>
       <c r="BO3" t="n">
-        <v>77.63636363636364</v>
+        <v>81.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>1.363636363636364</v>
+        <v>1.875</v>
       </c>
       <c r="BQ3" t="n">
-        <v>26.38095238095238</v>
+        <v>25.95</v>
       </c>
       <c r="BR3" t="n">
-        <v>183.7619047619048</v>
+        <v>181.95</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.9047619047619</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>16523.80952380952</v>
+        <v>26300</v>
       </c>
       <c r="BU3" t="n">
-        <v>1785714.285714286</v>
+        <v>4620000</v>
       </c>
       <c r="BV3" t="n">
-        <v>72.23809523809524</v>
+        <v>75.7</v>
       </c>
       <c r="BW3" t="n">
         <v>1</v>
       </c>
       <c r="BX3" t="n">
-        <v>26.84210526315789</v>
+        <v>22.3125</v>
       </c>
       <c r="BY3" t="n">
-        <v>182.1052631578947</v>
+        <v>184.9375</v>
       </c>
       <c r="BZ3" t="n">
-        <v>73.42105263157895</v>
+        <v>73.1875</v>
       </c>
       <c r="CA3" t="n">
-        <v>26631.57894736842</v>
+        <v>25937.5</v>
       </c>
       <c r="CB3" t="n">
-        <v>4515789.47368421</v>
+        <v>10518750</v>
       </c>
       <c r="CC3" t="n">
-        <v>75.26315789473684</v>
+        <v>81.375</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.052631578947368</v>
+        <v>1.25</v>
       </c>
       <c r="CE3" t="n">
-        <v>28</v>
+        <v>28.5</v>
       </c>
       <c r="CF3" t="n">
-        <v>185.3333333333333</v>
+        <v>181.5</v>
       </c>
       <c r="CG3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="CH3" t="n">
-        <v>210</v>
+        <v>298</v>
       </c>
       <c r="CI3" t="n">
-        <v>49000</v>
+        <v>125000</v>
       </c>
       <c r="CJ3" t="n">
-        <v>6100000</v>
+        <v>23600000</v>
       </c>
       <c r="CK3" t="n">
-        <v>219</v>
+        <v>301</v>
       </c>
       <c r="CL3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CM3" t="n">
-        <v>27.66666666666667</v>
+        <v>19</v>
       </c>
       <c r="CN3" t="n">
-        <v>182.3333333333333</v>
+        <v>172</v>
       </c>
       <c r="CO3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CP3" t="n">
-        <v>222</v>
+        <v>59</v>
       </c>
       <c r="CQ3" t="n">
-        <v>89000</v>
+        <v>3000</v>
       </c>
       <c r="CR3" t="n">
-        <v>17100000</v>
+        <v>575000</v>
       </c>
       <c r="CS3" t="n">
-        <v>225</v>
+        <v>76</v>
       </c>
       <c r="CT3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EVjKq6Vs</t>
+          <t>WQadeyWO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.35416666666</v>
+        <v>45592.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1534,862 +1548,878 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">sportpark ronhof thomas sommer
-  furth </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>16626</v>
+        <v>26000</v>
       </c>
       <c r="F4" t="n">
-        <v>16126</v>
+        <v>26000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="L4" t="n">
-        <v>3.38</v>
+        <v>2.23</v>
       </c>
       <c r="M4" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="N4" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
         <v>9</v>
       </c>
-      <c r="P4" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>4</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
         <v>7</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" t="n">
         <v>5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="n">
-        <v>19</v>
-      </c>
-      <c r="X4" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3</v>
       </c>
       <c r="AA4" t="n">
         <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AD4" t="n">
         <v>13</v>
       </c>
       <c r="AE4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>247</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>654</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>169</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>591</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR4" t="n">
         <v>3</v>
       </c>
-      <c r="AF4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="n">
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>591</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="n">
+        <v>27.44444444444444</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>186.4444444444445</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>71.55555555555556</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>16000</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2369444.444444444</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>74.44444444444444</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>27.55555555555556</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>184.8888888888889</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>84.77777777777777</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>87333.33333333333</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>56388888.88888889</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>86.55555555555556</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>3.555555555555555</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>26.78947368421053</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>185.6842105263158</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>68.57894736842105</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>16368.42105263158</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1647368.421052632</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>73.15789473684211</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>26.63157894736842</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>184.8947368421053</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>80.73684210526316</v>
+      </c>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="n">
+        <v>38525000</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>84</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>2.631578947368421</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>25.33333333333333</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>184</v>
+      </c>
+      <c r="CG4" t="n">
         <v>3</v>
       </c>
-      <c r="AL4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>496</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>379</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>422</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>296</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>8E86CPuD</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-      <c r="AW4" t="n">
-        <v>59</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>592</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>120</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>116</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>8200</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1572500</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
-      <c r="BK4" t="inlineStr"/>
-      <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="n">
-        <v>24.54545454545455</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>183.1363636363636</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>7818.181818181818</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>1494318.181818182</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>72.36363636363636</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>25.13333333333333</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>182.6</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>68.33333333333333</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>8333.333333333334</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>1794666.666666667</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>72.86666666666666</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>21</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>180</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>1</v>
-      </c>
       <c r="CH4" t="n">
-        <v>66</v>
+        <v>208</v>
       </c>
       <c r="CI4" t="n">
-        <v>6000</v>
+        <v>52000</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1600000</v>
+        <v>7875000</v>
       </c>
       <c r="CK4" t="n">
-        <v>73</v>
+        <v>219</v>
       </c>
       <c r="CL4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CM4" t="n">
-        <v>26</v>
+        <v>22.2</v>
       </c>
       <c r="CN4" t="n">
-        <v>182</v>
+        <v>185.8</v>
       </c>
       <c r="CO4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="CP4" t="n">
-        <v>68</v>
+        <v>368</v>
       </c>
       <c r="CQ4" t="n">
-        <v>9000</v>
+        <v>195000</v>
       </c>
       <c r="CR4" t="n">
-        <v>1500000</v>
+        <v>67150000</v>
       </c>
       <c r="CS4" t="n">
-        <v>71</v>
+        <v>412</v>
       </c>
       <c r="CT4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hOt0vBg2</t>
+          <t>Od8RJbU8</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.35416666666</v>
+        <v>45592.39583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">schwengers p 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksparkstadion
-  hamburg </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>57274</v>
+        <v>23325</v>
       </c>
       <c r="F5" t="n">
-        <v>57000</v>
+        <v>21809</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
         <v>1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>2.32</v>
+        <v>0.68</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="N5" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="O5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="X5" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
         <v>8</v>
       </c>
-      <c r="Y5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AJ5" t="n">
         <v>2</v>
       </c>
-      <c r="AG5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
       <c r="AK5" t="n">
-        <v>2</v>
+        <v>549</v>
       </c>
       <c r="AL5" t="n">
-        <v>2</v>
+        <v>407</v>
       </c>
       <c r="AM5" t="n">
-        <v>348</v>
+        <v>456</v>
       </c>
       <c r="AN5" t="n">
-        <v>549</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>278</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>519</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>EDRZkDzS</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>IgZoGKFn</t>
-        </is>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>SQrxFAMl</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>pdPRS0me</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>592</v>
       </c>
       <c r="AW5" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>592</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
         <v>20242025</v>
       </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="BB5" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="BC5" t="n">
-        <v>26.72727272727273</v>
+        <v>26.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>182.7272727272727</v>
+        <v>185.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>71.36363636363636</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>21090.90909090909</v>
+        <v>10600</v>
       </c>
       <c r="BG5" t="n">
-        <v>2563636.363636364</v>
+        <v>1375000</v>
       </c>
       <c r="BH5" t="n">
-        <v>73.72727272727273</v>
+        <v>71.7</v>
       </c>
       <c r="BI5" t="n">
         <v>1</v>
       </c>
       <c r="BJ5" t="n">
-        <v>26.77777777777778</v>
+        <v>26.44444444444444</v>
       </c>
       <c r="BK5" t="n">
-        <v>182.1111111111111</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="BL5" t="n">
-        <v>67.88888888888889</v>
+        <v>65.88888888888889</v>
       </c>
       <c r="BM5" t="n">
-        <v>10111.11111111111</v>
+        <v>7888.888888888889</v>
       </c>
       <c r="BN5" t="n">
-        <v>1291666.666666667</v>
+        <v>1016666.666666667</v>
       </c>
       <c r="BO5" t="n">
-        <v>70</v>
+        <v>68.66666666666667</v>
       </c>
       <c r="BP5" t="n">
         <v>1</v>
       </c>
       <c r="BQ5" t="n">
-        <v>24.25</v>
+        <v>25.90909090909091</v>
       </c>
       <c r="BR5" t="n">
-        <v>180.3333333333333</v>
+        <v>182.3181818181818</v>
       </c>
       <c r="BS5" t="n">
-        <v>69.33333333333333</v>
+        <v>66.13636363636364</v>
       </c>
       <c r="BT5" t="n">
-        <v>19666.66666666667</v>
+        <v>8772.727272727272</v>
       </c>
       <c r="BU5" t="n">
-        <v>2175000</v>
+        <v>1168409.090909091</v>
       </c>
       <c r="BV5" t="n">
-        <v>74.5</v>
+        <v>70.13636363636364</v>
       </c>
       <c r="BW5" t="n">
         <v>1</v>
       </c>
       <c r="BX5" t="n">
-        <v>24.60869565217391</v>
+        <v>27.6</v>
       </c>
       <c r="BY5" t="n">
-        <v>178.4347826086957</v>
+        <v>184.25</v>
       </c>
       <c r="BZ5" t="n">
-        <v>65.95652173913044</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="CA5" t="n">
-        <v>10782.60869565217</v>
+        <v>8950</v>
       </c>
       <c r="CB5" t="n">
-        <v>1190217.391304348</v>
+        <v>910000</v>
       </c>
       <c r="CC5" t="n">
-        <v>69.78260869565217</v>
+        <v>68.7</v>
       </c>
       <c r="CD5" t="n">
         <v>1</v>
       </c>
       <c r="CE5" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>190.4</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>332</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>44000</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>5700000</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>354</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>5</v>
+      </c>
+      <c r="CM5" t="n">
         <v>25.5</v>
       </c>
-      <c r="CF5" t="n">
-        <v>190.5</v>
-      </c>
-      <c r="CG5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CH5" t="n">
-        <v>134</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>41000</v>
-      </c>
-      <c r="CJ5" t="n">
-        <v>4625000</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>143</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>2</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>29</v>
-      </c>
       <c r="CN5" t="n">
-        <v>177</v>
+        <v>179.3333333333333</v>
       </c>
       <c r="CO5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CP5" t="n">
-        <v>70</v>
+        <v>394</v>
       </c>
       <c r="CQ5" t="n">
-        <v>12000</v>
+        <v>47000</v>
       </c>
       <c r="CR5" t="n">
-        <v>1400000</v>
+        <v>6750000</v>
       </c>
       <c r="CS5" t="n">
-        <v>70</v>
+        <v>417</v>
       </c>
       <c r="CT5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4rrbmRgU</t>
+          <t>Io8X1Q8N</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45585.35416666666</v>
+        <v>45592.39583333334</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">merck stadion am bollenfalltor
+  darmstadt </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19500</v>
+        <v>17810</v>
       </c>
       <c r="F6" t="n">
-        <v>17400</v>
+        <v>17455</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>tbC3EcQn</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
       <c r="K6" t="n">
-        <v>0.63</v>
+        <v>1.08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.38</v>
+        <v>0.62</v>
       </c>
       <c r="M6" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="N6" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
         <v>3</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="X6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AI6" t="n">
         <v>2</v>
       </c>
-      <c r="AG6" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>3</v>
+      </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>683</v>
       </c>
       <c r="AL6" t="n">
-        <v>3</v>
+        <v>316</v>
       </c>
       <c r="AM6" t="n">
-        <v>420</v>
+        <v>594</v>
       </c>
       <c r="AN6" t="n">
-        <v>474</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>349</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>408</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>4dKVOnA1</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
         <is>
           <t>QevvB2nf</t>
         </is>
       </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>OzPMRhK3</t>
-        </is>
+      <c r="AU6" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>592</v>
       </c>
       <c r="AW6" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>592</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
         <v>20242025</v>
       </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="BB6" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="BC6" t="n">
-        <v>27</v>
+        <v>25.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>186.5</v>
+        <v>187.125</v>
       </c>
       <c r="BE6" t="n">
-        <v>64.3</v>
+        <v>70.125</v>
       </c>
       <c r="BF6" t="n">
-        <v>7900</v>
+        <v>13250</v>
       </c>
       <c r="BG6" t="n">
-        <v>760000</v>
+        <v>2075000</v>
       </c>
       <c r="BH6" t="n">
-        <v>67.3</v>
+        <v>73.625</v>
       </c>
       <c r="BI6" t="n">
         <v>1</v>
       </c>
       <c r="BJ6" t="n">
-        <v>27.27272727272727</v>
+        <v>26.1</v>
       </c>
       <c r="BK6" t="n">
-        <v>184.1818181818182</v>
+        <v>184.8</v>
       </c>
       <c r="BL6" t="n">
-        <v>68.36363636363636</v>
+        <v>64.8</v>
       </c>
       <c r="BM6" t="n">
-        <v>10636.36363636364</v>
+        <v>5800</v>
       </c>
       <c r="BN6" t="n">
-        <v>1470454.545454545</v>
+        <v>882500</v>
       </c>
       <c r="BO6" t="n">
-        <v>72.36363636363636</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="BP6" t="n">
         <v>1</v>
       </c>
       <c r="BQ6" t="n">
-        <v>23.625</v>
+        <v>26</v>
       </c>
       <c r="BR6" t="n">
-        <v>183.125</v>
+        <v>183.2777777777778</v>
       </c>
       <c r="BS6" t="n">
-        <v>64.25</v>
+        <v>67.27777777777777</v>
       </c>
       <c r="BT6" t="n">
-        <v>7625</v>
+        <v>10833.33333333333</v>
       </c>
       <c r="BU6" t="n">
-        <v>1151875</v>
+        <v>1338888.888888889</v>
       </c>
       <c r="BV6" t="n">
-        <v>72</v>
+        <v>71.83333333333333</v>
       </c>
       <c r="BW6" t="n">
         <v>1</v>
       </c>
       <c r="BX6" t="n">
-        <v>24.7</v>
+        <v>24.18181818181818</v>
       </c>
       <c r="BY6" t="n">
-        <v>182.35</v>
+        <v>185.1363636363636</v>
       </c>
       <c r="BZ6" t="n">
-        <v>66.34999999999999</v>
+        <v>64.04545454545455</v>
       </c>
       <c r="CA6" t="n">
-        <v>11600</v>
+        <v>8318.181818181818</v>
       </c>
       <c r="CB6" t="n">
-        <v>1356750</v>
+        <v>1056363.636363636</v>
       </c>
       <c r="CC6" t="n">
-        <v>72.3</v>
+        <v>71.13636363636364</v>
       </c>
       <c r="CD6" t="n">
         <v>1</v>
       </c>
       <c r="CE6" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="CF6" t="n">
-        <v>187</v>
+        <v>183.4</v>
       </c>
       <c r="CG6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CH6" t="n">
-        <v>201</v>
+        <v>353</v>
       </c>
       <c r="CI6" t="n">
-        <v>15000</v>
+        <v>78000</v>
       </c>
       <c r="CJ6" t="n">
-        <v>2775000</v>
+        <v>7225000</v>
       </c>
       <c r="CK6" t="n">
-        <v>207</v>
+        <v>359</v>
       </c>
       <c r="CL6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="CM6" t="n">
-        <v>23</v>
+        <v>30.5</v>
       </c>
       <c r="CN6" t="n">
-        <v>184</v>
+        <v>190.5</v>
       </c>
       <c r="CO6" t="n">
         <v>2</v>
       </c>
       <c r="CP6" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="CQ6" t="n">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="CR6" t="n">
-        <v>1825000</v>
+        <v>1475000</v>
       </c>
       <c r="CS6" t="n">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="CT6" t="n">
         <v>2</v>
@@ -2398,75 +2428,73 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6o5TuOU6</t>
+          <t>AHQvdex2</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45584.64583333334</v>
+        <v>45592.39583333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz walter stadion
-  kaiserslautern </t>
+          <t xml:space="preserve">avnet arena
+  magdeburg </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>49500</v>
-      </c>
-      <c r="F7" t="n">
-        <v>41500</v>
-      </c>
+        <v>25910</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2.16</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="M7" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="N7" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="O7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="P7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T7" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
@@ -2474,225 +2502,221 @@
         <v>19</v>
       </c>
       <c r="X7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>24</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE7" t="n">
         <v>3</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>5</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AK7" t="n">
-        <v>3</v>
+        <v>587</v>
       </c>
       <c r="AL7" t="n">
-        <v>3</v>
+        <v>240</v>
       </c>
       <c r="AM7" t="n">
-        <v>289</v>
+        <v>499</v>
       </c>
       <c r="AN7" t="n">
-        <v>559</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>216</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>479</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr"/>
       <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>4bJLk19p</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>0AI1QUJH</t>
-        </is>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>IgZoGKFn</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>59</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>592</v>
       </c>
       <c r="AW7" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>592</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
         <v>20242025</v>
       </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="BB7" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="BC7" t="n">
-        <v>25.3</v>
+        <v>25.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>184.6</v>
+        <v>181.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>66.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>9000</v>
+        <v>10600</v>
       </c>
       <c r="BG7" t="n">
-        <v>1565000</v>
+        <v>1327500</v>
       </c>
       <c r="BH7" t="n">
-        <v>70.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="BI7" t="n">
         <v>1</v>
       </c>
       <c r="BJ7" t="n">
-        <v>25.8</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="BK7" t="n">
-        <v>184.6</v>
+        <v>183.6666666666667</v>
       </c>
       <c r="BL7" t="n">
-        <v>67.7</v>
+        <v>71.55555555555556</v>
       </c>
       <c r="BM7" t="n">
-        <v>13300</v>
+        <v>20333.33333333333</v>
       </c>
       <c r="BN7" t="n">
-        <v>1480000</v>
+        <v>2583333.333333333</v>
       </c>
       <c r="BO7" t="n">
-        <v>71.59999999999999</v>
+        <v>75.33333333333333</v>
       </c>
       <c r="BP7" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="BQ7" t="n">
-        <v>26.15</v>
+        <v>24.95</v>
       </c>
       <c r="BR7" t="n">
-        <v>179.15</v>
+        <v>177.7</v>
       </c>
       <c r="BS7" t="n">
-        <v>67.90000000000001</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>9900</v>
+        <v>10250</v>
       </c>
       <c r="BU7" t="n">
-        <v>1537500</v>
+        <v>1203750</v>
       </c>
       <c r="BV7" t="n">
-        <v>70.84999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="BW7" t="n">
         <v>1</v>
       </c>
       <c r="BX7" t="n">
-        <v>23.6</v>
+        <v>25.09523809523809</v>
       </c>
       <c r="BY7" t="n">
-        <v>184.45</v>
+        <v>184.0952380952381</v>
       </c>
       <c r="BZ7" t="n">
-        <v>64.59999999999999</v>
+        <v>67.85714285714286</v>
       </c>
       <c r="CA7" t="n">
-        <v>11650</v>
+        <v>18476.19047619048</v>
       </c>
       <c r="CB7" t="n">
-        <v>1106250</v>
+        <v>1759523.809523809</v>
       </c>
       <c r="CC7" t="n">
-        <v>71.5</v>
+        <v>72.42857142857143</v>
       </c>
       <c r="CD7" t="n">
         <v>1</v>
       </c>
       <c r="CE7" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="CF7" t="n">
-        <v>183.5</v>
+        <v>177</v>
       </c>
       <c r="CG7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CH7" t="n">
-        <v>411</v>
+        <v>70</v>
       </c>
       <c r="CI7" t="n">
-        <v>62000</v>
+        <v>12000</v>
       </c>
       <c r="CJ7" t="n">
-        <v>8150000</v>
+        <v>1400000</v>
       </c>
       <c r="CK7" t="n">
-        <v>420</v>
+        <v>70</v>
       </c>
       <c r="CL7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CM7" t="n">
-        <v>23.4</v>
+        <v>28</v>
       </c>
       <c r="CN7" t="n">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="CO7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CP7" t="n">
-        <v>331</v>
+        <v>69</v>
       </c>
       <c r="CQ7" t="n">
-        <v>55000</v>
+        <v>19000</v>
       </c>
       <c r="CR7" t="n">
-        <v>7225000</v>
+        <v>1300000</v>
       </c>
       <c r="CS7" t="n">
-        <v>366</v>
+        <v>69</v>
       </c>
       <c r="CT7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
